--- a/corpus/manifest/corpus_manifest.xlsx
+++ b/corpus/manifest/corpus_manifest.xlsx
@@ -1180,12 +1180,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -6628,17 +6628,17 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://data.safeworkaustralia.gov.au/interactive-data/topic/key-whs-statistics</t>
+          <t>https://www.safeworkaustralia.gov.au/data-and-research/work-related-fatalities/work-related-traumatic-injury-fatalities-database</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7122,20 +7122,24 @@
           <t>Abrasive Blasting Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>F2016L00417</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00417/asmade</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7219,20 +7223,24 @@
           <t>Confined Spaces Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>F2016L00405</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00405/asmade</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7316,10 +7324,14 @@
           <t>Construction Work Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>F2016L00394</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00394/asmade</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7329,7 +7341,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7413,10 +7425,14 @@
           <t>Demolition Work Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>F2016L00409</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00409/asmade</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7426,7 +7442,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7510,10 +7526,14 @@
           <t>Excavation Work Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>F2016L00416</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00416/asmade</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7523,7 +7543,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7607,10 +7627,14 @@
           <t>First Aid in the Workplace Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>F2016L00415</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00415/asmade</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7620,7 +7644,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7704,10 +7728,14 @@
           <t>Hazardous Manual Tasks Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>F2016L00406</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00406/asmade</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7717,7 +7745,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7801,10 +7829,14 @@
           <t>How to Manage and Control Asbestos in the Workplace Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>F2016L00423</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00423/asmade</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7814,7 +7846,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7898,10 +7930,14 @@
           <t>How to Manage Work Health and Safety Risks Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>F2016L00414</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00414/asmade</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7911,7 +7947,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7995,10 +8031,14 @@
           <t>How to Safely Remove Asbestos Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>F2016L00418</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00418/asmade</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8008,7 +8048,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8092,10 +8132,14 @@
           <t>Labelling of Workplace Hazardous Chemicals Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>F2016L00413</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00413/asmade</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8105,7 +8149,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8189,10 +8233,14 @@
           <t>Managing Electrical Risks in the Workplace Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>F2016L00407</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00407/asmade</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8202,7 +8250,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8286,10 +8334,14 @@
           <t>Managing Noise and Preventing Hearing Loss at Work Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>F2016L00426</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00426/asmade</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8299,7 +8351,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8383,20 +8435,24 @@
           <t>Managing Risks in Stevedoring Code of Practice 2017</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>F2017L01588</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2017L01588/asmade</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8480,10 +8536,14 @@
           <t>Managing Risks of Hazardous Chemicals in the Workplace Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>F2016L00420</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00420/asmade</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8493,7 +8553,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8577,10 +8637,14 @@
           <t>Managing Risks of Plant in the Workplace Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>F2016L00422</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00422/asmade</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8590,7 +8654,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8674,10 +8738,14 @@
           <t>Managing the Risk of Falls at Workplaces Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>F2016L00425</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00425/asmade</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8687,7 +8755,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8771,10 +8839,14 @@
           <t>Managing the Work Environment and Facilities Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>F2016L00421</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00421/asmade</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8784,7 +8856,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8868,10 +8940,14 @@
           <t>Preparation of Safety Data Sheets for Hazardous Chemicals Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>F2016L00424</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00424/asmade</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8881,7 +8957,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8965,10 +9041,14 @@
           <t>Preventing Falls in Housing Construction Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>F2016L00411</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00411/asmade</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8978,7 +9058,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9062,10 +9142,14 @@
           <t>Safe Design of Structures Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>F2016L00410</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00410/asmade</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9075,7 +9159,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9159,10 +9243,14 @@
           <t>Spray Painting and Powder Coating Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>F2016L00412</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00412/asmade</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9172,7 +9260,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9256,10 +9344,14 @@
           <t>Welding Processes Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>F2016L00419</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00419/asmade</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9269,7 +9361,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9571,20 +9663,24 @@
           <t>Work Health and Safety Consultation, Co-operation and Co-ordination Code of Practice 2015</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>F2016L00408</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/codes-of-practice</t>
+          <t>https://www.legislation.gov.au/F2016L00408/asmade</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9676,12 +9772,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9769,12 +9865,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9862,12 +9958,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9955,12 +10051,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10234,12 +10330,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10327,12 +10423,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10415,17 +10511,17 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.comcare.gov.au/scheme-legislation/regulating-scheme/regulatory-guides/prohibition-notices</t>
+          <t>https://www.comcare.gov.au/scheme-legislation/whs-act/regulatory-guides/prohibition-notices</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10513,12 +10609,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10606,12 +10702,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10699,12 +10795,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10885,12 +10981,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -10978,12 +11074,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -11071,12 +11167,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11164,12 +11260,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -11257,12 +11353,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -11350,12 +11446,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -11536,12 +11632,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11629,12 +11725,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -11931,17 +12027,17 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0017/52145/Abrasive-blasting-COP.pdf</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -12036,17 +12132,17 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0014/1404023/Collection_and_transport_of_waste-COP.pdf</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -12141,17 +12237,17 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0015/50073/Confined-spaces-COP.pdf</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -12246,17 +12342,17 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0014/52151/Construction-work-COP.pdf</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -12351,17 +12447,17 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0015/52161/Demolition-work-COP.pdf</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -12456,17 +12552,17 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0019/52147/Excavation-work-COP.pdf</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -12561,17 +12657,17 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0015/52152/First-aid-in-the-workplace-COP.pdf</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -12666,17 +12762,17 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0004/845887/Formwork-code-of-practice.pdf</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -12771,17 +12867,17 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0020/50078/Hazardous-manual-tasks-COP.pdf</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -12876,17 +12972,17 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0014/1400027/Healthcare-and-social-assistance-industry-COP.pdf</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -12981,17 +13077,17 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0014/50081/How-to-manage-and-control-asbestos-in-the-workplace-Code-of-Practice.pdf</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -13086,17 +13182,17 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0016/1411423/How_to_manage_BBV_exposure_risks_in_the_workplace-COP.pdf</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13187,17 +13283,17 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0012/50070/How-to-manage-work-health-and-safety-risks-COP.pdf</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13292,17 +13388,17 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0015/50082/How-to-safely-remove-asbestos-Code-of-Practice.pdf</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -13397,17 +13493,17 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0016/50083/Labelling-of-workplace-hazardous-chemicals-COP.pdf</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -13502,17 +13598,17 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0010/50230/Managing-electrical-risks-in-the-workplace-COP.pdf</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -13607,17 +13703,17 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0017/50075/Managing-noise-and-preventing-hearing-loss-at-work-COP.pdf</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -13712,17 +13808,17 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0004/983353/Code-of-Practice_Managing-psychosocial-hazards.pdf</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -13817,17 +13913,17 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0006/326940/Managing-Risks-in-Stevedoring-Code-of-Practice-SW08622.pdf</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -13922,17 +14018,17 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0018/50076/Managing-the-risk-of-falls-at-workplaces-COP.pdf</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -14027,17 +14123,17 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0018/52155/Managing-risks-of-hazardous-chemicals-in-the-workplace-COP.pdf</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -14132,17 +14228,17 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0012/1400034/Managing-risks-of-RCS-COP.pdf</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -14237,17 +14333,17 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0005/79160/SW08262-Code-of-Practice-Managing-risks-when-new-or-inexperienced-riders-or-handlers-interact-with-horses-in-the-workplace.pdf</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -14342,17 +14438,17 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0020/52157/Managing-the-risk-of-falls-in-housing-construction-COP.pdf</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -14447,17 +14543,17 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0015/1400028/Managing-fatigue-at-work-COP.pdf</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -14552,17 +14648,17 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0019/52156/Code-of-practice_Managing-the-risks-of-plant-in-the-workplace_2022.pdf</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -14657,17 +14753,17 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0016/50074/Managing-the-work-environment-and-facilities.pdf</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -14762,17 +14858,17 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0009/1394838/moving-plant-on-construction-sites-cop.pdf</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -14964,17 +15060,17 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0017/50084/Code-of-practice_Preparation_of_safety_data_sheets_for_hazardous_chemicals_2022.pdf</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -15069,17 +15165,17 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0003/52158/Safe-design-of-structures-COP.pdf</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -15174,17 +15270,17 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0017/1404026/Safe_handling_of_timber_preservatives-COP.pdf</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -15279,17 +15375,17 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0011/1411499/Safe_use_and_design_of_bulk_storage_silos_and_bins-COP.pdf</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -15380,17 +15476,17 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0013/1404022/Agricultural_and_veterinary_chemicals-COP.pdf</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -15485,17 +15581,17 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0010/1394704/safety-in-forest-harvesting-COP.pdf</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -15586,17 +15682,17 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0017/1411424/Sawmilling_industry-COP.pdf</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -15687,17 +15783,17 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0010/1310131/Code-of-Practice-Sexual-and-gender-based-harassment.pdf</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -15788,17 +15884,17 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0004/52159/Code-of-practice_Spray-painting-and-powder-coating_2022.pdf</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -15893,17 +15989,17 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0004/1375816/Code_of_practice_Tower_Cranes_2025.pdf</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -15994,17 +16090,17 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0018/1411425/Transport_and_delivery_of_cash_and_valuables-COP.pdf</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -16095,17 +16191,17 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0018/1404027/Tree_work-COP.pdf</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -16196,17 +16292,17 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0007/52873/Tunnels-Under-Construction-Code-of-Practice.pdf</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -16297,17 +16393,17 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0014/52160/Code-of-practice_Welding-processes_2022.pdf</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -16402,17 +16498,17 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0013/50071/Code-of-practice_WHS-consultation-cooperation-and-coordination_February-2022.pdf</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -16507,17 +16603,17 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0004/1411429/Work_near_electric_lines-COP.pdf</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -16608,17 +16704,17 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0019/1411435/Work-on-roofs-COP.pdf</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -16709,17 +16805,17 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0014/1411430/Worker-accommodation-COP.pdf</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -16810,17 +16906,17 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.safework.nsw.gov.au/resource-library/list-of-all-codes-of-practice</t>
+          <t>https://www.safework.nsw.gov.au/__data/assets/pdf_file/0017/1411433/Working_safely-COP.pdf</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -20811,12 +20907,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -20908,12 +21004,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -21005,12 +21101,12 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -21316,12 +21412,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -21413,12 +21509,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -21510,12 +21606,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -21607,12 +21703,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -21704,12 +21800,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -21792,7 +21888,7 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0024/72627/abrasive-blasting-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -21802,7 +21898,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -21897,7 +21993,7 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/laws-and-compliance/codes-of-practice/amusement-devices-code-of-practice-2023</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -21907,7 +22003,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -21998,7 +22094,7 @@
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0019/130906/cane-rail-safety-supplement-sugar-mill-safety-code-of-practice-2024.pdf</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -22008,7 +22104,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -22099,7 +22195,7 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0020/18227/cash-in-transit-cop-2011.pdf</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -22109,7 +22205,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -22200,7 +22296,7 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0016/20068/children-young-workers-cop-2006.pdf</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -22210,7 +22306,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -22301,7 +22397,7 @@
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0019/18127/concrete-pumping-cop-2019.pdf</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -22311,7 +22407,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -22402,7 +22498,7 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0025/72628/confined-spaces-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -22412,7 +22508,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -22503,7 +22599,7 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0016/23506/construction-and-operation-of-solar-farms-cop.pdf</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -22513,7 +22609,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -23311,7 +23407,7 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0014/18113/forest-harvesting-cop-2007.pdf</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -23321,7 +23417,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -23412,7 +23508,7 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0019/15823/formwork-cop-2016.pdf</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -23422,7 +23518,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -23513,7 +23609,7 @@
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0020/15914/foundry-cop-2004.pdf</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -23523,7 +23619,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -23614,7 +23710,7 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0020/72632/hazardous-manual-tasks-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -23624,7 +23720,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -23715,7 +23811,7 @@
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0023/17096/horse-riding-cop-2002.pdf</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -23725,7 +23821,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -23816,7 +23912,7 @@
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0021/72633/how-to-manage-control-asbestos-in-the-workplace-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -23826,7 +23922,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -23917,7 +24013,7 @@
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0022/72634/how-to-manage-work-health-and-safety-risks-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -23927,7 +24023,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -24018,7 +24114,7 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0023/72635/how-to-safely-remove-asbestos-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -24028,7 +24124,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -24119,7 +24215,7 @@
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0024/72636/labelling-workplace-hazardous-chemicals-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -24129,7 +24225,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -24220,7 +24316,7 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0026/72638/managing-noise-hearing-loss-at-work-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -24230,7 +24326,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -24321,7 +24417,7 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/laws-and-compliance/codes-of-practice/managing-respirable-crystalline-silica-dust-exposure-in-construction-and-manufacturing-of-construction-elements-code-of-practice-2022</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -24331,7 +24427,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -24422,7 +24518,7 @@
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/laws-and-compliance/codes-of-practice/managing-respirable-dust-hazards-in-coal-fired-power-stations-code-of-practice-2023</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -24432,7 +24528,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -24523,7 +24619,7 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0014/23603/managing-risks-in-stevedoring-code-of-practice.pdf</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -24533,7 +24629,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -24624,7 +24720,7 @@
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0027/72639/managing-risks-of-hazardous-chemicals-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -24634,7 +24730,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -24725,7 +24821,7 @@
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0019/72640/managing-the-risk-of-falls-at-workplaces-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -24735,7 +24831,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -24826,7 +24922,7 @@
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/laws-and-compliance/codes-of-practice/managing-the-risk-of-psychosocial-hazards-at-work-code-of-practice-2022</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -24836,7 +24932,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -24927,7 +25023,7 @@
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0020/72641/managing-the-risks-of-plant-in-the-workplace-cop-2021-1.pdf</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -24937,7 +25033,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -25129,7 +25225,7 @@
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0015/21525/manual-tasks-people-handling-cop-2001.pdf</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -25139,7 +25235,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -25230,7 +25326,7 @@
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0018/130950/mobile-crane-code-of-practice-2024.pdf</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -25240,7 +25336,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -25331,7 +25427,7 @@
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0006/21030/occupational-diving-work-cop-2005.pdf</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -25341,7 +25437,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -25432,7 +25528,7 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0022/72643/preparation-safety-data-sheets-hazardous-chemicals-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -25442,7 +25538,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -25533,7 +25629,7 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0031/129676/recreational-diving-code-of-practice-2024.pdf</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -25543,7 +25639,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -25634,7 +25730,7 @@
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0019/130447/rural-plant-code-of-practice-2024.pdf</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -25644,7 +25740,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -25735,7 +25831,7 @@
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0023/72644/safe-design-of-structures-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -25745,7 +25841,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -25836,7 +25932,7 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0027/76347/scaffolding-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -25846,7 +25942,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -25937,7 +26033,7 @@
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0024/72645/spray-painting-powder-coating-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -25947,7 +26043,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -26038,7 +26134,7 @@
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0017/19115/steel-construction-cop-2004.pdf</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -26048,7 +26144,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -26139,7 +26235,7 @@
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0018/130842/sugar-mill-safety-code-of-practice-2024.pdf</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -26149,7 +26245,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -26240,7 +26336,7 @@
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0015/18060/tilt-up-pre-cast-cop-2003.pdf</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -26250,7 +26346,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -26341,7 +26437,7 @@
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0021/20991/tower-crane-code-of-practice-2017.pdf</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -26351,7 +26447,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -26442,7 +26538,7 @@
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0018/22158/traffic-management-construction-cop-2008.pdf</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -26452,7 +26548,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -26543,7 +26639,7 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0025/72646/welding-processes-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -26553,7 +26649,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -26644,7 +26740,7 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.business.qld.gov.au/running-business/whs/whs-laws/codes-practice</t>
+          <t>https://www.worksafe.qld.gov.au/__data/assets/pdf_file/0026/72647/whs-consultation-cooperation-coordination-cop-2021.pdf</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -26654,7 +26750,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -30401,7 +30497,7 @@
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>https://www.safework.sa.gov.au/about-us/annual-activity-report</t>
+          <t>https://www.safework.sa.gov.au/about-us/2024-25-annual-activity-report/overview</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -30411,7 +30507,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -30918,17 +31014,17 @@
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-abrasive-blasting-0</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -31019,17 +31115,17 @@
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-concrete-and-masonry-cutting-and-drilling</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -31112,17 +31208,17 @@
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/confined-spaces-code-practice</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -31213,17 +31309,17 @@
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-construction-work</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -31314,17 +31410,17 @@
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-control-noise-music-entertainment-industry</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -31407,17 +31503,17 @@
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-demolition-work</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -31508,17 +31604,17 @@
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/emergency-management-western-australian-mines-code-practice</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
@@ -31601,17 +31697,17 @@
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-excavation</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
@@ -31694,17 +31790,17 @@
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-fatigue-management-commercial-vehicle-drivers</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
@@ -31787,17 +31883,17 @@
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-first-aid-workplace</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
@@ -31888,17 +31984,17 @@
       <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/ground-control-western-australian-mining-operations-code-practice</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
@@ -32086,17 +32182,17 @@
       <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-how-manage-and-control-asbestos-workplace</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -32292,17 +32388,17 @@
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-how-safely-remove-asbestos</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -32393,17 +32489,17 @@
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-labelling-workplace-hazardous-chemicals</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -32494,17 +32590,17 @@
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-man-overboard-prevention-and-response</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -32587,17 +32683,17 @@
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/managing-electrical-risks-workplace-code-practice</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -32688,17 +32784,17 @@
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-managing-noise-and-preventing-hearing-loss-work</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
@@ -32789,17 +32885,17 @@
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-managing-risks-stevedoring</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
@@ -32895,12 +32991,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
@@ -32991,17 +33087,17 @@
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/managing-risks-plant-workplace-code-practice</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -33092,17 +33188,17 @@
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/managing-risk-falls-workplaces-code-practice</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -33193,17 +33289,17 @@
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-managing-risk-falls-housing-construction</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
@@ -33299,12 +33395,12 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
@@ -33395,17 +33491,17 @@
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/mentally-healthy-workplaces-fly-fly-out-fifo-workers-resources-and-construction-sectors</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -33493,12 +33589,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
@@ -33589,17 +33685,17 @@
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/mineral-exploration-drilling-code-practice</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
@@ -33687,12 +33783,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
@@ -33775,17 +33871,17 @@
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/dangerous-goods-codes-practice-and-guidance</t>
+          <t>https://www.worksafe.wa.gov.au/publications/minimising-risk-tyre-fires-when-transporting-ammonium-nitrate-explosion-risk-goods</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
@@ -33868,17 +33964,17 @@
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-occupational-safety-and-health-call-centres</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -33961,17 +34057,17 @@
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-occupational-safety-and-health-western-australian-public-sector</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -34054,17 +34150,17 @@
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-preparation-safety-data-sheets-hazardous-chemicals</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
@@ -34155,17 +34251,17 @@
       <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-prevention-and-control-legionnaires-disease</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
@@ -34248,17 +34344,17 @@
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-psychosocial-hazards-workplace</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
@@ -34349,17 +34445,17 @@
       <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-safe-design-structures</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
@@ -34450,17 +34546,17 @@
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/safe-mobile-autonomous-mining-western-australia-code-practice</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -34543,17 +34639,17 @@
       <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/dangerous-goods-codes-practice-and-guidance</t>
+          <t>https://www.worksafe.wa.gov.au/publications/safe-storage-solid-ammonium-nitrate-code-practice</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
@@ -34636,17 +34732,17 @@
       <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/dangerous-goods-codes-practice-and-guidance</t>
+          <t>https://www.worksafe.wa.gov.au/publications/safe-use-close-proximity-fireworks-western-australia-code-practice</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
@@ -34729,17 +34825,17 @@
       <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/dangerous-goods-codes-practice-and-guidance</t>
+          <t>https://www.worksafe.wa.gov.au/publications/safe-use-outdoor-fireworks-western-australia-code-practice</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -34822,17 +34918,17 @@
       <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-spray-painting-and-powder-coating</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -34923,17 +35019,17 @@
       <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/surface-rock-support-underground-mine-code-practice</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -35016,17 +35112,17 @@
       <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/tailing-storage-facilities-western-australia-code-practice</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
@@ -35109,17 +35205,17 @@
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/tower-cranes-code-practice</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -35210,17 +35306,17 @@
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-violence-and-aggression-work</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -35311,17 +35407,17 @@
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-welding-processes</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -35412,17 +35508,17 @@
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-work-health-and-safety-consultation-cooperation-and-coordination</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -35518,12 +35614,12 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -35606,17 +35702,17 @@
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
-          <t>https://www.worksafe.wa.gov.au/work-health-and-safety-and-transitional-codes-practice</t>
+          <t>https://www.worksafe.wa.gov.au/publications/code-practice-workplace-behaviour</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
@@ -40772,17 +40868,17 @@
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr">
         <is>
-          <t>https://legislation.nt.gov.au/Legislation/DANGEROUS-GOODS-ACT-1998</t>
+          <t>https://legislation.nt.gov.au/api/sitecore/Act/PDF?id=11752</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -43164,7 +43260,7 @@
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
-          <t>https://worksafe.nt.gov.au/forms-and-resources/codes-of-practice</t>
+          <t>https://worksafe.nt.gov.au/forms-and-resources/codes-of-practice/preparation-of-safety-data-sheets-for-hazardous-chemicals</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -43174,7 +43270,7 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -43977,10 +44073,14 @@
           <t>Work Health and Safety (Abrasive Blasting Code of Practice) Approval 2022</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>NI2022-682</t>
+        </is>
+      </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-682/</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -44074,10 +44174,14 @@
           <t>Work Health and Safety (Confined Spaces Code of Practice) Approval 2025</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>NI2025-443</t>
+        </is>
+      </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-443/</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -44171,10 +44275,14 @@
           <t>Work Health and Safety (Construction Work Code of Practice) Approval 2025</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>NI2025-446</t>
+        </is>
+      </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-446/</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -44268,10 +44376,14 @@
           <t>Work Health and Safety (Demolition Work Code of Practice) Approval 2020</t>
         </is>
       </c>
-      <c r="F444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>NI2020-541</t>
+        </is>
+      </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2020-541/</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -44365,10 +44477,14 @@
           <t>Work Health and Safety (Excavation Work Code of Practice) Approval 2020</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>NI2020-542</t>
+        </is>
+      </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2020-542/</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -44462,10 +44578,14 @@
           <t>Work Health and Safety (First Aid in the Workplace Code of Practice) Approval 2020</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>NI2020-543</t>
+        </is>
+      </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2020-543/</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -44559,10 +44679,14 @@
           <t>Work Health and Safety (Formwork) Code of Practice 2024</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>NI2024-56</t>
+        </is>
+      </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2024-56/</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -44656,20 +44780,24 @@
           <t>Work Health and Safety (Hazardous Manual Tasks Code of Practice) Approval 2020</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>NI2020-544</t>
+        </is>
+      </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2020-544/</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -44753,10 +44881,14 @@
           <t>Work Health and Safety (How to Manage and Control Asbestos in the Workplace Code of Practice) Approval 2022</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>NI2022-691</t>
+        </is>
+      </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-691/</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -44850,10 +44982,14 @@
           <t>Work Health and Safety (How to Manage Work Health and Safety Risks) Code of Practice Approval 2025</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>NI2025-442</t>
+        </is>
+      </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-442/</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -44947,10 +45083,14 @@
           <t>Work Health and Safety (How to Safely Remove Asbestos Code of Practice) Approval 2022</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>NI2022-690</t>
+        </is>
+      </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-690/</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -45044,10 +45184,14 @@
           <t>Work Health and Safety (Labelling of Workplace Hazardous Chemicals Code of Practice) Approval 2022</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>NI2022-689</t>
+        </is>
+      </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-689/</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -45141,10 +45285,14 @@
           <t>Work Health and Safety (Managing Electrical Risks at the Workplace Code of Practice) Approval 2020</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>NI2020-556</t>
+        </is>
+      </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2020-556/</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -45238,10 +45386,14 @@
           <t>Work Health and Safety (Managing Noise and Preventing Hearing Loss at Work) Code of Practice 2025</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>NI2025-440</t>
+        </is>
+      </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-440/</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -45335,10 +45487,14 @@
           <t>Work Health and Safety (Managing Psychosocial Hazards at Work Code of Practice) Approval 2023</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>NI2023-482</t>
+        </is>
+      </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2023-482/</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -45432,10 +45588,14 @@
           <t>Work Health and Safety (Managing risks of hazardous chemicals in the workplace Code of Practice) Approval 2022</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>NI2022-687</t>
+        </is>
+      </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-687/</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -45529,10 +45689,14 @@
           <t>Work Health and Safety (Managing Risks of Plant in the Workplace Code of Practice) Approval 2025</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>NI2025-445</t>
+        </is>
+      </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-445/</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -45626,10 +45790,14 @@
           <t>Work Health and Safety (Managing the Risk of Falls at Workplaces Code of Practice) Approval 2020</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>NI2020-553</t>
+        </is>
+      </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2020-553/</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -45723,10 +45891,14 @@
           <t>Work Health and Safety (Managing the Risk of Falls in Housing Construction Code of Practice) Approval 2020</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>NI2020-552</t>
+        </is>
+      </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2020-552/</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -45820,20 +45992,24 @@
           <t>Work Health and Safety (Managing the Risks Associated with Extreme Temperatures Code of Practice) Approval 2025</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>NI2025-607</t>
+        </is>
+      </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-607/</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -45917,20 +46093,24 @@
           <t>Work Health and Safety (Managing the Risks of Airborne Crystalline Silica (Silica Dust) in the Workplace Code of Practice) Approval 2024</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>NI2024-339</t>
+        </is>
+      </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2024-339/</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -46014,10 +46194,14 @@
           <t>Work Health and Safety (Managing the Work Environment and Facilities Code of Practice) Approval 2025</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>NI2025-444</t>
+        </is>
+      </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-444/</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -46111,10 +46295,14 @@
           <t>Work Health and Safety (Preparation of safety data sheets for hazardous chemicals Code of Practice) Approval 2022</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>NI2022-686</t>
+        </is>
+      </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-686/</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -46208,20 +46396,24 @@
           <t>Work Health and Safety (Safe Design of Structures Code of Practice) Approval 2025</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>NI2025-506</t>
+        </is>
+      </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-506/</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -46305,10 +46497,14 @@
           <t>Work Health and Safety (Sex Work Code of Practice) Approval 2023</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>NI2023-631</t>
+        </is>
+      </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2023-631/</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -46402,10 +46598,14 @@
           <t>Work Health and Safety (Sexual and gender-based harassment) Code of Practice Approval 2024</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>NI2024-399</t>
+        </is>
+      </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2024-399/</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -46499,10 +46699,14 @@
           <t>Work Health and Safety (Spray Painting and Powder Coating Code of Practice) 2022</t>
         </is>
       </c>
-      <c r="F467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>NI2022-685</t>
+        </is>
+      </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-685/</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -46596,10 +46800,14 @@
           <t>Work Health and Safety (Tower Crane) Code of Practice Approval 2025</t>
         </is>
       </c>
-      <c r="F468" t="inlineStr"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>NI2025-173</t>
+        </is>
+      </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2025-173/</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -46693,20 +46901,24 @@
           <t>Work Health and Safety (Transport and Delivery of Cash) Code of Practice 2011</t>
         </is>
       </c>
-      <c r="F469" t="inlineStr"/>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>NI2011-771</t>
+        </is>
+      </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2011-771/</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -46790,10 +47002,14 @@
           <t>Work Health and Safety (Welding Process Code of Practice) Approval 2022</t>
         </is>
       </c>
-      <c r="F470" t="inlineStr"/>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>NI2022-683</t>
+        </is>
+      </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2022-683/</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -46887,10 +47103,14 @@
           <t>Work Health and Safety (Work Health and Safety Consultation, Cooperation and Coordination Code of Practice) Approval 2023</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>NI2023-632</t>
+        </is>
+      </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/laws-and-compliance/codes-of-practice</t>
+          <t>https://legislation.act.gov.au/ni/2023-632/</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -46987,7 +47207,7 @@
       <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0003/2036154/Cleaning-of-Mr-Fluffy-Demolition-Vehicles.pdf</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -47080,7 +47300,7 @@
       <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0003/2036163/Consulting-with-your-worker-about-COVID-19.pdf</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -47173,7 +47393,7 @@
       <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0005/2036165/CRYSTALLINE-SILICA-DUST.pdf</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -47266,7 +47486,7 @@
       <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0019/2036251/ELECTRICAL-HAZARDS-WHEN-WORKING-IN-CEILING-SPACES.pdf</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -47359,7 +47579,7 @@
       <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/laws-and-compliance/enforcement-and-prosecutions/enforceable-undertakings/guidance-note-enforceable-undertakings-information-for-auditors</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -47452,7 +47672,7 @@
       <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/laws-and-compliance/enforcement-and-prosecutions/enforceable-undertakings/guidance-note-enforceable-undertakings-information-for-injured-persons,-next-of-kin-or-guardians</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -47545,7 +47765,7 @@
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0004/2517385/ACT-Engineered-stone-prohibition-guidance-for-PCBUs-Updated.pdf</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -47638,7 +47858,7 @@
       <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0007/2036167/Entry-permit-holders-obligations.pdf</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -47731,7 +47951,7 @@
       <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0009/2036169/Entry-permit-holders-rights-and-responsibilities.pdf</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -47824,7 +48044,7 @@
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0020/2036171/Exempt-Essential-Workers-COVID-19.pdf</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -47917,7 +48137,7 @@
       <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0008/2036195/WORKPLACE-RIGHT-OF-ENTRY-BY-WORK-HEALTH-AND-SAFETY-ENTRY-PERMIT-HOLDERS-.pdf</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -48010,7 +48230,7 @@
       <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0011/1814339/HIGH-LOW-LIFTS-Updated-June-2024.pdf</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -48103,7 +48323,7 @@
       <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0007/2036185/WORKERS-COMPENSATION-AND-LABOUR-HIRE.pdf</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -48196,7 +48416,7 @@
       <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0008/2036177/LONG-SERVICE-LEAVE-1.pdf</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -48289,7 +48509,7 @@
       <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0008/2036177/LONG-SERVICE-LEAVE-1.pdf</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -48382,7 +48602,7 @@
       <c r="F487" t="inlineStr"/>
       <c r="G487" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0010/2036179/Managing-silica-dust-at-construction-sites.pdf</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -48475,7 +48695,7 @@
       <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0003/2036181/PACKAGING-FOR-ALCOHOL-BASED-HAND-SANITISERS-.pdf</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -48568,7 +48788,7 @@
       <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0005/2578982/final-Guidance-Note-supervision-of-apprentices-002.pdf</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -48661,7 +48881,7 @@
       <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0005/2036183/TRANSPORT-OF-WASTE-CONTAINING-ASBESTOS.pdf</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -48754,7 +48974,7 @@
       <c r="F491" t="inlineStr"/>
       <c r="G491" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0006/2036175/LOCKING-MECHANISMS-ON-TWO-POST-VEHICLE-HOISTS.pdf</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -48847,7 +49067,7 @@
       <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0004/2036191/WORKERS-COMPENSATION-Employer-Obligations.pdf</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -48940,7 +49160,7 @@
       <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0009/2036187/WORKERS-COMPENSATION-APPROVAL-AS-A-SELF-INSURER-IN-THE-ACT.pdf</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -49033,7 +49253,7 @@
       <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0011/2036189/WORKERS-COMPENSATION-EMPLOYER-OBLIGATIONS-2.pdf</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -49126,7 +49346,7 @@
       <c r="F495" t="inlineStr"/>
       <c r="G495" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/health-and-safety-portal/safety-topics/safety-advice/guidance-notes</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0006/2036193/WORKING-SAFELY-WITH-ASBESTOS-CONTAINING-MATERIALS.pdf</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -49219,7 +49439,7 @@
       <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/about-worksafe-act/publications</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0010/1908667/WorkSafe-ACT-annual-report-2020-2021.PDF</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -49316,7 +49536,7 @@
       <c r="F497" t="inlineStr"/>
       <c r="G497" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/about-worksafe-act/publications</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0003/2090037/WorkSafe-ACT-Annual-Report-21-22-Final.pdf</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -49413,7 +49633,7 @@
       <c r="F498" t="inlineStr"/>
       <c r="G498" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/about-worksafe-act/publications</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0016/2307040/WorkSafe-ACT-Annual-Report-22-23-Final-corrected.pdf</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -49510,7 +49730,7 @@
       <c r="F499" t="inlineStr"/>
       <c r="G499" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/about-worksafe-act/publications</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0011/2616968/Worksafe-ACT-23-24-Annual-Report-compressed.pdf</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -49607,7 +49827,7 @@
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/about-worksafe-act/publications</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0010/2931085/2024-25-Office-of-the-Work-Health-and-Safety-Commissioner-AR-website.pdf</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -49704,7 +49924,7 @@
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr">
         <is>
-          <t>https://www.worksafe.act.gov.au/about-worksafe-act/publications</t>
+          <t>https://www.worksafe.act.gov.au/__data/assets/pdf_file/0007/1635541/getting-home-safely-report.pdf</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -53223,17 +53443,17 @@
       <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/asbestos-safe-work-instrument/</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
@@ -53316,17 +53536,17 @@
       <c r="F537" t="inlineStr"/>
       <c r="G537" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/hazardous-substances/</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -53409,17 +53629,17 @@
       <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/general-risk-and-workplace-management-safe-work-instrument/</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
@@ -53502,17 +53722,17 @@
       <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/mining-operations-and-quarrying-operations-safe-work-instruments/</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
@@ -53595,17 +53815,17 @@
       <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/pipelines-safe-work-instrument/</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
@@ -54072,17 +54292,17 @@
       <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/managing-health-and-safety/businesses/general-requirements-for-workplaces/general-risk-and-workplace-management-part-1/</t>
+          <t>https://www.worksafe.govt.nz/assets/dmsassets/WKS-3-general-risk-and-workplace-management-part-2.pdf</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
@@ -54267,12 +54487,12 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">

--- a/corpus/manifest/corpus_manifest.xlsx
+++ b/corpus/manifest/corpus_manifest.xlsx
@@ -10,7 +10,7 @@
     <sheet name="corpus_manifest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'corpus_manifest'!$A$1:$W$691</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'corpus_manifest'!$A$1:$W$692</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W691"/>
+  <dimension ref="A1:W692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30089,7 +30089,7 @@
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
-          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0004/1392520/model-cop-preventing-falls-in-housing-construction.pdf</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -30104,7 +30104,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -30149,7 +30149,7 @@
       <c r="V298" t="inlineStr"/>
       <c r="W298" t="inlineStr">
         <is>
-          <t>Residential-falls COP; high value given SA's 1 Jul 2026 HRCW &gt;2m threshold. Per-document URL pending. Added per 2026-06-30 gap review.</t>
+          <t>Residential-falls COP; high value given SA's 1 Jul 2026 HRCW &gt;2m threshold. Per-document URL pending. Added per 2026-06-30 gap review. Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch).</t>
         </is>
       </c>
     </row>
@@ -30182,7 +30182,7 @@
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0003/136272/Managing-risks-in-stevedoring.pdf</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -30242,7 +30242,7 @@
       <c r="V299" t="inlineStr"/>
       <c r="W299" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch).</t>
         </is>
       </c>
     </row>
@@ -30275,7 +30275,7 @@
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safeworkaustralia.gov.au/system/files/documents/1702/codeofpractice_precasttiltupandconcreteelementsbuildingconstruction_2008_pdf.pdf</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -30290,7 +30290,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -30335,7 +30335,7 @@
       <c r="V300" t="inlineStr"/>
       <c r="W300" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch). SA index links to the SWA-hosted national code PDF (2008).</t>
         </is>
       </c>
     </row>
@@ -30368,7 +30368,7 @@
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0020/145640/Tuna-farm-diving.pdf</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -30383,7 +30383,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -30428,7 +30428,7 @@
       <c r="V301" t="inlineStr"/>
       <c r="W301" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch).</t>
         </is>
       </c>
     </row>
@@ -30461,7 +30461,7 @@
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://library.safework.sa.gov.au/attachments/53098/ACOP%20working%20hours.pdf</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -30476,7 +30476,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -30521,7 +30521,7 @@
       <c r="V302" t="inlineStr"/>
       <c r="W302" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch). SafeWork SA Library-hosted PDF.</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0011/1391069/model_cop_elevatingworkplatforms-december2025.pdf</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       <c r="V303" t="inlineStr"/>
       <c r="W303" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch). Filename suggests December 2025 edition (VERIFY).</t>
         </is>
       </c>
     </row>
@@ -30647,7 +30647,7 @@
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0003/1391070/model_code_of_practice_for_the_healthcare_and_social_assistance_industry.pdf</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -30662,7 +30662,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -30707,7 +30707,7 @@
       <c r="V304" t="inlineStr"/>
       <c r="W304" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch).</t>
         </is>
       </c>
     </row>
@@ -30740,7 +30740,7 @@
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0007/1391065/modelcop_managing_risks_biological_hazards_mar2026.pdf</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -30755,7 +30755,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -30800,7 +30800,7 @@
       <c r="V305" t="inlineStr"/>
       <c r="W305" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch). Filename suggests March 2026 edition (VERIFY).</t>
         </is>
       </c>
     </row>
@@ -30833,7 +30833,7 @@
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0003/1385463/modelcop_fatigue_sept2025.pdf</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -30848,7 +30848,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -30893,7 +30893,7 @@
       <c r="V306" t="inlineStr"/>
       <c r="W306" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch). Filename suggests September 2025 edition (VERIFY).</t>
         </is>
       </c>
     </row>
@@ -30926,7 +30926,7 @@
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/__data/assets/pdf_file/0005/1392521/modelcop_managing-risks-respirable-crystalline-silica_nov2025.pdf</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -30986,7 +30986,7 @@
       <c r="V307" t="inlineStr"/>
       <c r="W307" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on SafeWork SA approved-codes index (live-verified 2026-07-02, headed browser). Direct PDF URL resolved 2026-07-02 from the live SafeWork SA approved-codes index (headed browser; site blocks plain automated fetch). Filename suggests November 2025 edition (VERIFY).</t>
         </is>
       </c>
     </row>
@@ -31338,7 +31338,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -31402,7 +31402,7 @@
       <c r="V311" t="inlineStr"/>
       <c r="W311" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -31439,7 +31439,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -31503,7 +31503,7 @@
       <c r="V312" t="inlineStr"/>
       <c r="W312" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -31604,7 +31604,7 @@
       <c r="V313" t="inlineStr"/>
       <c r="W313" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -31705,7 +31705,7 @@
       <c r="V314" t="inlineStr"/>
       <c r="W314" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -31742,7 +31742,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -31806,7 +31806,7 @@
       <c r="V315" t="inlineStr"/>
       <c r="W315" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -31907,7 +31907,7 @@
       <c r="V316" t="inlineStr"/>
       <c r="W316" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -31944,7 +31944,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -32008,7 +32008,7 @@
       <c r="V317" t="inlineStr"/>
       <c r="W317" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -32045,7 +32045,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -32109,7 +32109,7 @@
       <c r="V318" t="inlineStr"/>
       <c r="W318" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -32146,7 +32146,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -32210,7 +32210,7 @@
       <c r="V319" t="inlineStr"/>
       <c r="W319" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -32311,7 +32311,7 @@
       <c r="V320" t="inlineStr"/>
       <c r="W320" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -32348,7 +32348,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>https://safework.sa.gov.au/resources/codes-of-practice</t>
+          <t>https://www.safework.sa.gov.au/resources/codes-of-practice</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -32412,7 +32412,7 @@
       <c r="V321" t="inlineStr"/>
       <c r="W321" t="inlineStr">
         <is>
-          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia. Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
+          <t>SafeWork SA official codes page lists this standard as an approved Code of Practice in South Australia (live-verified 2026-07-02, headed browser). Standard text is not openly licensed; edition/part details should be verified against the SafeWork SA Library/Standards catalogue before citation.</t>
         </is>
       </c>
     </row>
@@ -37867,7 +37867,7 @@
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -37904,7 +37904,7 @@
       <c r="V377" t="inlineStr"/>
       <c r="W377" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on WorkSafe WA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; live-verified 2026-07-02 as listed under 'Industry codes of practice' on the WorkSafe WA index. Formal status under the WHS Act 2020 not stated on the page - currency VERIFY. Direct document URL not resolved in this pass.</t>
         </is>
       </c>
     </row>
@@ -37960,7 +37960,7 @@
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -37997,7 +37997,7 @@
       <c r="V378" t="inlineStr"/>
       <c r="W378" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on WorkSafe WA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; live-verified 2026-07-02 as listed under 'Industry codes of practice' on the WorkSafe WA index. Formal status under the WHS Act 2020 not stated on the page - currency VERIFY. Direct document URL not resolved in this pass.</t>
         </is>
       </c>
     </row>
@@ -38053,7 +38053,7 @@
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -38090,7 +38090,7 @@
       <c r="V379" t="inlineStr"/>
       <c r="W379" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on WorkSafe WA codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; live-verified 2026-07-02 as listed under 'Industry codes of practice' on the WorkSafe WA index. Formal status under the WHS Act 2020 not stated on the page - currency VERIFY. Direct document URL not resolved in this pass.</t>
         </is>
       </c>
     </row>
@@ -38158,7 +38158,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -38195,7 +38195,7 @@
       <c r="V380" t="inlineStr"/>
       <c r="W380" t="inlineStr">
         <is>
-          <t>Official WorkSafe WA publication page direct-fetched via search result; page states publication type Code of practice and last updated 19 Nov 2024. Included as a WA-specific approved legacy code reference for blood-borne virus exposure.</t>
+          <t>Official WorkSafe WA publication page direct-fetched via search result; page states publication type Code of practice and last updated 19 Nov 2024. Hosted WorkSafe WA publication (type: Code of practice) but NOT listed on the WA codes-of-practice index (live-checked 2026-07-02); approval status under the WHS Act 2020 unconfirmed - legacy national NOHSC code. date_published sourced from page metadata (VERIFY).</t>
         </is>
       </c>
     </row>
@@ -38255,7 +38255,7 @@
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -38296,7 +38296,7 @@
       <c r="V381" t="inlineStr"/>
       <c r="W381" t="inlineStr">
         <is>
-          <t>Listed by WorkSafe WA as an industry code of practice. Standard text is paywalled/restricted; use as citation metadata only unless a standards licence is obtained.</t>
+          <t>Listed by WorkSafe WA as an industry code of practice (live-verified 2026-07-02); formal status under the WHS Act 2020 not stated on the index page - currency VERIFY. Standard text is paywalled/restricted; use as citation metadata only unless a standards licence is obtained.</t>
         </is>
       </c>
     </row>
@@ -38356,7 +38356,7 @@
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -38397,7 +38397,7 @@
       <c r="V382" t="inlineStr"/>
       <c r="W382" t="inlineStr">
         <is>
-          <t>Listed by WorkSafe WA as an industry code of practice. Standard text is paywalled/restricted; use as citation metadata only unless a standards licence is obtained.</t>
+          <t>Listed by WorkSafe WA as an industry code of practice (live-verified 2026-07-02); formal status under the WHS Act 2020 not stated on the index page - currency VERIFY. Standard text is paywalled/restricted; use as citation metadata only unless a standards licence is obtained.</t>
         </is>
       </c>
     </row>
@@ -46355,7 +46355,7 @@
       <c r="V464" t="inlineStr"/>
       <c r="W464" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index (live-verified 2026-07-02, headed browser). Direct document URL not resolved in this pass.</t>
         </is>
       </c>
     </row>
@@ -46452,7 +46452,7 @@
       <c r="V465" t="inlineStr"/>
       <c r="W465" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index (live-verified 2026-07-02, headed browser). Direct document URL not resolved in this pass.</t>
         </is>
       </c>
     </row>
@@ -46549,7 +46549,7 @@
       <c r="V466" t="inlineStr"/>
       <c r="W466" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index (live-verified 2026-07-02, headed browser). Direct document URL not resolved in this pass.</t>
         </is>
       </c>
     </row>
@@ -46646,7 +46646,7 @@
       <c r="V467" t="inlineStr"/>
       <c r="W467" t="inlineStr">
         <is>
-          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index. Direct document URL not resolved in this pass.</t>
+          <t>Added after 2026-07-02 official regulator-index validation; listed on NT WorkSafe codes-of-practice index (live-verified 2026-07-02, headed browser). Direct document URL not resolved in this pass.</t>
         </is>
       </c>
     </row>
@@ -59363,7 +59363,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>NZ-GPG-001</t>
+          <t>NZ-ACOP-053</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -59378,28 +59378,32 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>good_practice_guideline</t>
+          <t>acop</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Best Practice Guidelines for Working at Height in New Zealand</t>
-        </is>
-      </c>
-      <c r="F598" t="inlineStr"/>
+          <t>New Zealand Electrical Code of Practice for electrical safe distances (NZECP 34: 2001)</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>NZECP 34:2001</t>
+        </is>
+      </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/500-best-practice-guidelines-for-working-at-height-in-new-zealand</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/1565-new-zealand-electrical-code-of-practice-for-electrical-safe-distances-nzecp-34-2001/</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
@@ -59412,17 +59416,17 @@
       <c r="M598" t="inlineStr"/>
       <c r="N598" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>FALLS</t>
+          <t>ELECTRICAL</t>
         </is>
       </c>
       <c r="P598" t="inlineStr">
         <is>
-          <t>CONSTRUCTION,ALL</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q598" t="inlineStr">
@@ -59449,14 +59453,14 @@
       <c r="V598" t="inlineStr"/>
       <c r="W598" t="inlineStr">
         <is>
-          <t>Search confirms dmsdocument/500 'Best practice guidelines for working at height in New Zealand'. Hierarchy: eliminate/isolate/minimise; covers fall protection, scaffolding, ladders, harnesses. Companion fact sheets exist (e.g. dmsdocument/503 planning, dmsdocument/509 equipment selection). Mapped FALLS. Crown copyright, attribution required.</t>
+          <t>Added 2026-07-02 after source audit found it missing from the NZECP set. Listed on the WorkSafe NZ electricity-codes-of-practice page alongside NZECP 35-60; direct PDF URL verified live (HTTP 200 application/pdf). Most widely used NZECP - sets minimum safe electrical distances for overhead lines; referenced by the Electricity (Safety) Regulations 2010 (VERIFY exact provision). Electrical safety regime currency requires verification; confirm against the live WorkSafe page before relying on a clause.</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>NZ-GPG-002</t>
+          <t>NZ-GPG-001</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -59476,13 +59480,13 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Conducting asbestos surveys – Good practice guidelines for asbestos surveyors</t>
+          <t>Best Practice Guidelines for Working at Height in New Zealand</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
       <c r="G599" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/asbestos/conducting-asbestos-surveys-good-practice-guidelines-for-asbestos-surveyors/</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/500-best-practice-guidelines-for-working-at-height-in-new-zealand</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -59510,7 +59514,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FALLS</t>
         </is>
       </c>
       <c r="P599" t="inlineStr">
@@ -59542,14 +59546,14 @@
       <c r="V599" t="inlineStr"/>
       <c r="W599" t="inlineStr">
         <is>
-          <t>WorkSafe GPG for asbestos surveyors (planning, carrying out and reporting management / refurbishment-demolition surveys). Part of the refreshed asbestos guidance suite alongside the 2016 Asbestos ACOP. Slug normalised to '...good-practice-guidelines...' (enumerator title said 'guidance'). Mapped CHEMICAL. VERIFY exact slug against the asbestos topic index. Crown copyright, attribution required.</t>
+          <t>Search confirms dmsdocument/500 'Best practice guidelines for working at height in New Zealand'. Hierarchy: eliminate/isolate/minimise; covers fall protection, scaffolding, ladders, harnesses. Companion fact sheets exist (e.g. dmsdocument/503 planning, dmsdocument/509 equipment selection). Mapped FALLS. Crown copyright, attribution required.</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>NZ-GPG-003</t>
+          <t>NZ-GPG-002</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -59569,23 +59573,23 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Confined spaces: planning entry and working safely in a confined space</t>
+          <t>Conducting asbestos surveys – Good practice guidelines for asbestos surveyors</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
       <c r="G600" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/confined-spaces-planning-entry-and-working-safely-in-a-confined-space/</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/asbestos/conducting-asbestos-surveys-good-practice-guidelines-for-asbestos-surveyors/</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
@@ -59603,12 +59607,12 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>CONFINED_SPACES</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P600" t="inlineStr">
         <is>
-          <t>MANUFACTURING,CONSTRUCTION,ALL</t>
+          <t>CONSTRUCTION,ALL</t>
         </is>
       </c>
       <c r="Q600" t="inlineStr">
@@ -59635,14 +59639,14 @@
       <c r="V600" t="inlineStr"/>
       <c r="W600" t="inlineStr">
         <is>
-          <t>CORRECTION: page fetched OK (200) but this is NOT a full 'Good Practice Guidelines' — it is a short WorkSafe QUICK GUIDE (~181KB PDF) summarising the standard. WorkSafe endorses AS 2865 Confined spaces as the current state of knowledge and states the quick guide is not a substitute for the standard. Removed the '– Good Practice Guidelines' suffix from the title to avoid overstating its status. Mapped CONFINED_SPACES. Note AS 2865 itself is a third-party AS/NZS standard (copyright Standards Australia/NZ) and is NOT covered by the crown-copyright-open licence — do not ingest the standard text.</t>
+          <t>WorkSafe GPG for asbestos surveyors (planning, carrying out and reporting management / refurbishment-demolition surveys). Part of the refreshed asbestos guidance suite alongside the 2016 Asbestos ACOP. Slug normalised to '...good-practice-guidelines...' (enumerator title said 'guidance'). Mapped CHEMICAL. VERIFY exact slug against the asbestos topic index. Crown copyright, attribution required.</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>NZ-GPG-004</t>
+          <t>NZ-GPG-003</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -59662,13 +59666,13 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Excavation safety – Good Practice Guidelines</t>
+          <t>Confined spaces: planning entry and working safely in a confined space</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
       <c r="G601" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/excavation/excavation-safety-gpg/</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/confined-spaces-planning-entry-and-working-safely-in-a-confined-space/</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -59696,12 +59700,12 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>FALLS</t>
+          <t>CONFINED_SPACES</t>
         </is>
       </c>
       <c r="P601" t="inlineStr">
         <is>
-          <t>CONSTRUCTION,ALL</t>
+          <t>MANUFACTURING,CONSTRUCTION,ALL</t>
         </is>
       </c>
       <c r="Q601" t="inlineStr">
@@ -59728,14 +59732,14 @@
       <c r="V601" t="inlineStr"/>
       <c r="W601" t="inlineStr">
         <is>
-          <t>WorkSafe GPG for excavation work (collapse prevention by shore/bench/batter, access/egress, underground services). Page fetched OK (200); PDF ~5MB; cites AS 2865 and AS 4744. Mapped FALLS (excavation edge fall-in / collapse). Publication date not displayed on page. Crown copyright, attribution required.</t>
+          <t>CORRECTION: page fetched OK (200) but this is NOT a full 'Good Practice Guidelines' — it is a short WorkSafe QUICK GUIDE (~181KB PDF) summarising the standard. WorkSafe endorses AS 2865 Confined spaces as the current state of knowledge and states the quick guide is not a substitute for the standard. Removed the '– Good Practice Guidelines' suffix from the title to avoid overstating its status. Mapped CONFINED_SPACES. Note AS 2865 itself is a third-party AS/NZS standard (copyright Standards Australia/NZ) and is NOT covered by the crown-copyright-open licence — do not ingest the standard text.</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>NZ-GPG-005</t>
+          <t>NZ-GPG-004</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -59755,23 +59759,23 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Exposure monitoring and health monitoring – Good Practice Guidelines</t>
+          <t>Excavation safety – Good Practice Guidelines</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
       <c r="G602" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/monitoring/guidance-for-businesses/</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/excavation/excavation-safety-gpg/</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
@@ -59789,12 +59793,12 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FALLS</t>
         </is>
       </c>
       <c r="P602" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION,ALL</t>
         </is>
       </c>
       <c r="Q602" t="inlineStr">
@@ -59821,14 +59825,14 @@
       <c r="V602" t="inlineStr"/>
       <c r="W602" t="inlineStr">
         <is>
-          <t>WorkSafe monitoring guidance (selecting providers; exposure/health monitoring programmes), pairs with the WES/BEI. Exact title/slug not independently re-confirmed this pass; the /topic-and-industry/monitoring/ topic is live. Mapped CHEMICAL. VERIFY the precise document title and slug against the WorkSafe monitoring topic index. Crown copyright, attribution required.</t>
+          <t>WorkSafe GPG for excavation work (collapse prevention by shore/bench/batter, access/egress, underground services). Page fetched OK (200); PDF ~5MB; cites AS 2865 and AS 4744. Mapped FALLS (excavation edge fall-in / collapse). Publication date not displayed on page. Crown copyright, attribution required.</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>NZ-GPG-006</t>
+          <t>NZ-GPG-005</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -59848,13 +59852,13 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Managing electrical risk at work – WorkSafe guidance (Electricity topic)</t>
+          <t>Exposure monitoring and health monitoring – Good Practice Guidelines</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
       <c r="G603" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/electricity/</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/monitoring/guidance-for-businesses/</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -59864,12 +59868,12 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K603" t="inlineStr"/>
@@ -59877,17 +59881,17 @@
       <c r="M603" t="inlineStr"/>
       <c r="N603" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>ELECTRICAL</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P603" t="inlineStr">
         <is>
-          <t>CONSTRUCTION,ALL</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q603" t="inlineStr">
@@ -59914,14 +59918,14 @@
       <c r="V603" t="inlineStr"/>
       <c r="W603" t="inlineStr">
         <is>
-          <t>WorkSafe electricity topic landing (managing electrical risk; construction sites/farms). IMPORTANT: NZ electrical safety sits under the Electricity (Safety) Regulations 2010 + Electrical Codes of Practice (ECP) — a SEPARATE statutory regime from HSWA, administered with Energy Safety; catalogue specific ECPs separately if in scope. Catalogued at regulator-index level; individual artefact URLs unresolved. Mapped ELECTRICAL. Crown copyright (WorkSafe pages); attribution required.  [gap-review] Placeholder topic-index URL — resolve to a specific electrical GPG or remove; NZ electrical safety largely sits under a separate Energy Safety regime.</t>
+          <t>WorkSafe monitoring guidance (selecting providers; exposure/health monitoring programmes), pairs with the WES/BEI. Exact title/slug not independently re-confirmed this pass; the /topic-and-industry/monitoring/ topic is live. Mapped CHEMICAL. VERIFY the precise document title and slug against the WorkSafe monitoring topic index. Crown copyright, attribution required.</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>NZ-GPG-007</t>
+          <t>NZ-GPG-006</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -59941,13 +59945,13 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Preventing and responding to bullying at work – Good Practice Guidelines</t>
+          <t>Managing electrical risk at work – WorkSafe guidance (Electricity topic)</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
       <c r="G604" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/782-preventing-and-responding-to-bullying-at-work</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/electricity/</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -59957,38 +59961,30 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>regulator_index</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="K604" t="inlineStr">
-        <is>
-          <t>2014-02</t>
-        </is>
-      </c>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr"/>
-      <c r="M604" t="inlineStr">
-        <is>
-          <t>2017-03</t>
-        </is>
-      </c>
+      <c r="M604" t="inlineStr"/>
       <c r="N604" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>PSYCHOSOCIAL</t>
+          <t>ELECTRICAL</t>
         </is>
       </c>
       <c r="P604" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION,ALL</t>
         </is>
       </c>
       <c r="Q604" t="inlineStr">
@@ -60015,14 +60011,14 @@
       <c r="V604" t="inlineStr"/>
       <c r="W604" t="inlineStr">
         <is>
-          <t>Search confirms dmsdocument/782 'Preventing and responding to bullying at work' — guidelines first published Feb 2014, updated Mar 2017 (added these dates). A companion worker-facing doc exists at dmsdocument/785. Mapped PSYCHOSOCIAL per node rules (bullying). NOTE: pre-dates current psychosocial-risk thinking — VERIFY it has not been superseded by newer WorkSafe psychosocial guidance before relying on specifics. Crown copyright, attribution required.</t>
+          <t>WorkSafe electricity topic landing (managing electrical risk; construction sites/farms). IMPORTANT: NZ electrical safety sits under the Electricity (Safety) Regulations 2010 + Electrical Codes of Practice (ECP) — a SEPARATE statutory regime from HSWA, administered with Energy Safety; catalogue specific ECPs separately if in scope. Catalogued at regulator-index level; individual artefact URLs unresolved. Mapped ELECTRICAL. Crown copyright (WorkSafe pages); attribution required.  [gap-review] Placeholder topic-index URL — resolve to a specific electrical GPG or remove; NZ electrical safety largely sits under a separate Energy Safety regime.</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>NZ-GPG-008</t>
+          <t>NZ-GPG-007</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -60042,23 +60038,23 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Scaffolding in New Zealand – Good Practice Guidelines</t>
+          <t>Preventing and responding to bullying at work – Good Practice Guidelines</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
       <c r="G605" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/working-at-height/scaffolding-in-new-zealand/</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/782-preventing-and-responding-to-bullying-at-work</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
@@ -60068,13 +60064,13 @@
       </c>
       <c r="K605" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="L605" t="inlineStr"/>
       <c r="M605" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
@@ -60084,12 +60080,12 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>FALLS</t>
+          <t>PSYCHOSOCIAL</t>
         </is>
       </c>
       <c r="P605" t="inlineStr">
         <is>
-          <t>CONSTRUCTION</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q605" t="inlineStr">
@@ -60116,14 +60112,14 @@
       <c r="V605" t="inlineStr"/>
       <c r="W605" t="inlineStr">
         <is>
-          <t>WorkSafe GPG 'Scaffolding in New Zealand' on safe design, use and maintenance. Page fetched OK (200); PDF ~11MB. Mapped FALLS (scaffold = working at height). Nov 2016 date is from the enumerator; not displayed on the live page — treat as approximate. Crown copyright, attribution required.</t>
+          <t>Search confirms dmsdocument/782 'Preventing and responding to bullying at work' — guidelines first published Feb 2014, updated Mar 2017 (added these dates). A companion worker-facing doc exists at dmsdocument/785. Mapped PSYCHOSOCIAL per node rules (bullying). NOTE: pre-dates current psychosocial-risk thinking — VERIFY it has not been superseded by newer WorkSafe psychosocial guidance before relying on specifics. Crown copyright, attribution required.</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>NZ-GPG-009</t>
+          <t>NZ-GPG-008</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -60143,33 +60139,41 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Working on roofs – Good Practice Guidelines</t>
+          <t>Scaffolding in New Zealand – Good Practice Guidelines</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
       <c r="G606" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/working-at-height/roofs/working-on-roofs-gpg/</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/working-at-height/scaffolding-in-new-zealand/</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>HTML</t>
-        </is>
-      </c>
-      <c r="K606" t="inlineStr"/>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr"/>
-      <c r="M606" t="inlineStr"/>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
       <c r="N606" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -60209,14 +60213,14 @@
       <c r="V606" t="inlineStr"/>
       <c r="W606" t="inlineStr">
         <is>
-          <t>WorkSafe GPG on roof work, under the working-at-height suite. URL pattern not independently re-fetched in this pass (working-at-height topic confirmed live); plausible official location. Mapped FALLS. Publication date not stated. VERIFY the exact /roofs/ slug resolves; if not, fall back to the working-at-height topic index. Crown copyright, attribution required.</t>
+          <t>WorkSafe GPG 'Scaffolding in New Zealand' on safe design, use and maintenance. Page fetched OK (200); PDF ~11MB. Mapped FALLS (scaffold = working at height). Nov 2016 date is from the enumerator; not displayed on the live page — treat as approximate. Crown copyright, attribution required.</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>NZ-GPG-010</t>
+          <t>NZ-GPG-009</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -60236,13 +60240,13 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Managing psychosocial risks at work (Good Practice Guidelines)</t>
+          <t>Working on roofs – Good Practice Guidelines</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
       <c r="G607" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/70098-managing-psychosocial-risks-at-work/latest/</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/working-at-height/roofs/working-on-roofs-gpg/</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -60257,14 +60261,10 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="K607" t="inlineStr">
-        <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr"/>
       <c r="M607" t="inlineStr"/>
       <c r="N607" t="inlineStr">
@@ -60274,17 +60274,17 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>PSYCHOSOCIAL</t>
+          <t>FALLS</t>
         </is>
       </c>
       <c r="P607" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION</t>
         </is>
       </c>
       <c r="Q607" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R607" t="inlineStr">
@@ -60306,14 +60306,14 @@
       <c r="V607" t="inlineStr"/>
       <c r="W607" t="inlineStr">
         <is>
-          <t>Current NZ psychosocial GPG (Apr 2025). Added per 2026-06-30 gap review.</t>
+          <t>WorkSafe GPG on roof work, under the working-at-height suite. URL pattern not independently re-fetched in this pass (working-at-height topic confirmed live); plausible official location. Mapped FALLS. Publication date not stated. VERIFY the exact /roofs/ slug resolves; if not, fall back to the working-at-height topic index. Crown copyright, attribution required.</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>NZ-GPG-011</t>
+          <t>NZ-GPG-010</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -60333,13 +60333,13 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Asbestos removal — Good Practice Guidelines</t>
+          <t>Managing psychosocial risks at work (Good Practice Guidelines)</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
       <c r="G608" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/72531-asbestos-removal/latest/</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/70098-managing-psychosocial-risks-at-work/latest/</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -60359,7 +60359,7 @@
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="L608" t="inlineStr"/>
@@ -60371,7 +60371,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>PSYCHOSOCIAL</t>
         </is>
       </c>
       <c r="P608" t="inlineStr">
@@ -60381,7 +60381,7 @@
       </c>
       <c r="Q608" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R608" t="inlineStr">
@@ -60403,14 +60403,14 @@
       <c r="V608" t="inlineStr"/>
       <c r="W608" t="inlineStr">
         <is>
-          <t>Refreshed asbestos GPG suite.</t>
+          <t>Current NZ psychosocial GPG (Apr 2025). Added per 2026-06-30 gap review.</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>NZ-GPG-012</t>
+          <t>NZ-GPG-011</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -60430,13 +60430,13 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>Asbestos assessments — Good Practice Guidelines</t>
+          <t>Asbestos removal — Good Practice Guidelines</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
       <c r="G609" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/72529-asbestos-assessments/latest/</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/72531-asbestos-removal/latest/</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -60454,7 +60454,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr"/>
       <c r="M609" t="inlineStr"/>
       <c r="N609" t="inlineStr">
@@ -60496,14 +60500,14 @@
       <c r="V609" t="inlineStr"/>
       <c r="W609" t="inlineStr">
         <is>
-          <t>Companion GPG in the refreshed asbestos suite.</t>
+          <t>Refreshed asbestos GPG suite.</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>NZ-SWI-001</t>
+          <t>NZ-GPG-012</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -60518,33 +60522,33 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>safe_work_instrument</t>
+          <t>good_practice_guideline</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Asbestos Safe Work Instrument (HSWA)</t>
+          <t>Asbestos assessments — Good Practice Guidelines</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
       <c r="G610" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/asbestos-safe-work-instrument/</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/72529-asbestos-assessments/latest/</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K610" t="inlineStr"/>
@@ -60567,7 +60571,7 @@
       </c>
       <c r="Q610" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R610" t="inlineStr">
@@ -60577,7 +60581,7 @@
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>nz-legislation-public-domain-s27</t>
+          <t>crown-copyright-open-attribution</t>
         </is>
       </c>
       <c r="T610" t="inlineStr">
@@ -60589,14 +60593,14 @@
       <c r="V610" t="inlineStr"/>
       <c r="W610" t="inlineStr">
         <is>
-          <t>HSWA subordinate-legislation class (was entirely absent); per-document URL pending. Added per 2026-06-30 gap review.</t>
+          <t>Companion GPG in the refreshed asbestos suite.</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>NZ-SWI-002</t>
+          <t>NZ-SWI-001</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -60616,13 +60620,13 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Hazardous Substances Safe Work Instrument (HSWA)</t>
+          <t>Asbestos Safe Work Instrument (HSWA)</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
       <c r="G611" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/hazardous-substances/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/asbestos-safe-work-instrument/</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -60682,14 +60686,14 @@
       <c r="V611" t="inlineStr"/>
       <c r="W611" t="inlineStr">
         <is>
-          <t>HSWA SWI; per-document URL pending. Added per 2026-06-30 gap review.</t>
+          <t>HSWA subordinate-legislation class (was entirely absent); per-document URL pending. Added per 2026-06-30 gap review.</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>NZ-SWI-003</t>
+          <t>NZ-SWI-002</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -60709,13 +60713,13 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>General Risk and Workplace Management Safe Work Instrument (HSWA)</t>
+          <t>Hazardous Substances Safe Work Instrument (HSWA)</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
       <c r="G612" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/general-risk-and-workplace-management-safe-work-instrument/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/hazardous-substances/</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -60743,7 +60747,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P612" t="inlineStr">
@@ -60782,7 +60786,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>NZ-SWI-004</t>
+          <t>NZ-SWI-003</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -60802,13 +60806,13 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Mining Operations and Quarrying Operations Safe Work Instrument (HSWA)</t>
+          <t>General Risk and Workplace Management Safe Work Instrument (HSWA)</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
       <c r="G613" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/mining-operations-and-quarrying-operations-safe-work-instruments/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/general-risk-and-workplace-management-safe-work-instrument/</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -60841,7 +60845,7 @@
       </c>
       <c r="P613" t="inlineStr">
         <is>
-          <t>MINING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q613" t="inlineStr">
@@ -60875,7 +60879,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>NZ-SWI-005</t>
+          <t>NZ-SWI-004</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -60895,13 +60899,13 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Health and Safety in Employment (Pipelines) Safe Work Instrument 2023</t>
+          <t>Mining Operations and Quarrying Operations Safe Work Instrument (HSWA)</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
       <c r="G614" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/pipelines-safe-work-instrument/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/mining-operations-and-quarrying-operations-safe-work-instruments/</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -60919,11 +60923,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+      <c r="K614" t="inlineStr"/>
       <c r="L614" t="inlineStr"/>
       <c r="M614" t="inlineStr"/>
       <c r="N614" t="inlineStr">
@@ -60938,7 +60938,7 @@
       </c>
       <c r="P614" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>MINING</t>
         </is>
       </c>
       <c r="Q614" t="inlineStr">
@@ -60972,7 +60972,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>NZ-GUI-001</t>
+          <t>NZ-SWI-005</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -60987,36 +60987,40 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>guidance</t>
+          <t>safe_work_instrument</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Introduction to the Health and Safety at Work Act 2015 — special guide</t>
+          <t>Health and Safety in Employment (Pipelines) Safe Work Instrument 2023</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
       <c r="G615" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/824-introduction-to-the-health-and-safety-at-work-act-2015-special-guide/</t>
+          <t>https://www.worksafe.govt.nz/laws-and-regulations/safe-work-instruments/pipelines-safe-work-instrument/</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="K615" t="inlineStr"/>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr"/>
       <c r="M615" t="inlineStr"/>
       <c r="N615" t="inlineStr">
@@ -61046,7 +61050,7 @@
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>crown-copyright-open-attribution</t>
+          <t>nz-legislation-public-domain-s27</t>
         </is>
       </c>
       <c r="T615" t="inlineStr">
@@ -61058,14 +61062,14 @@
       <c r="V615" t="inlineStr"/>
       <c r="W615" t="inlineStr">
         <is>
-          <t>Plain-English HSWA orientation. Added per 2026-06-30 gap review.</t>
+          <t>HSWA SWI; per-document URL pending. Added per 2026-06-30 gap review.</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>NZ-GUI-002</t>
+          <t>NZ-GUI-001</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -61085,13 +61089,13 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Reasonably practicable (WorkSafe special guide)</t>
+          <t>Introduction to the Health and Safety at Work Act 2015 — special guide</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
       <c r="G616" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/848-reasonably-practicable/</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/824-introduction-to-the-health-and-safety-at-work-act-2015-special-guide/</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -61151,14 +61155,14 @@
       <c r="V616" t="inlineStr"/>
       <c r="W616" t="inlineStr">
         <is>
-          <t>SFAIRP two-step test (s22/s30). Added per 2026-06-30 gap review.</t>
+          <t>Plain-English HSWA orientation. Added per 2026-06-30 gap review.</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>NZ-GUI-003</t>
+          <t>NZ-GUI-002</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -61178,13 +61182,13 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Workplace Exposure Standards (WES) and Biological Exposure Indices (BEI), 15th edition</t>
+          <t>Reasonably practicable (WorkSafe special guide)</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
       <c r="G617" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/topic-and-industry/monitoring/workplace-exposure-standards-and-biological-exposure-indices/</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/848-reasonably-practicable/</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -61202,17 +61206,9 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
+      <c r="K617" t="inlineStr"/>
       <c r="L617" t="inlineStr"/>
-      <c r="M617" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
+      <c r="M617" t="inlineStr"/>
       <c r="N617" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -61220,7 +61216,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P617" t="inlineStr">
@@ -61230,7 +61226,7 @@
       </c>
       <c r="Q617" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R617" t="inlineStr">
@@ -61252,14 +61248,14 @@
       <c r="V617" t="inlineStr"/>
       <c r="W617" t="inlineStr">
         <is>
-          <t>Search confirms the 15th edition, effective February 2025 (PDF at dmsdocument/62251, ~1.4MB; topic index URL retained as it is stable). WorkSafe-set WES/BEI risk criteria for airborne hazardous substances; used for health risk assessment under the Hazardous Substances Regulations 2017. document_type=standard (WorkSafe-set exposure standard, NOT an ISO/AS-NZS standard) — so the crown-copyright-open licence DOES apply (unlike third-party AS/NZS standards). Mapped CHEMICAL. Attribution required.  [gap-review] Reclassified standard-&gt;guidance: free WorkSafe NZ Crown publication (NZ WES/BEI), not a paywalled ISO/AS standard.</t>
+          <t>SFAIRP two-step test (s22/s30). Added per 2026-06-30 gap review.</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>NZ-GUI-004</t>
+          <t>NZ-GUI-003</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -61279,13 +61275,13 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>WorkSafe position on officers' due diligence</t>
+          <t>Workplace Exposure Standards (WES) and Biological Exposure Indices (BEI), 15th edition</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
       <c r="G618" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/dmsdocument/1058-worksafe-position-on-officers-due-diligence</t>
+          <t>https://www.worksafe.govt.nz/topic-and-industry/monitoring/workplace-exposure-standards-and-biological-exposure-indices/</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -61303,9 +61299,17 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr"/>
-      <c r="M618" t="inlineStr"/>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
       <c r="N618" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -61313,7 +61317,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P618" t="inlineStr">
@@ -61345,14 +61349,14 @@
       <c r="V618" t="inlineStr"/>
       <c r="W618" t="inlineStr">
         <is>
-          <t>s44 HSWA officer due-diligence standard of care.</t>
+          <t>Search confirms the 15th edition, effective February 2025 (PDF at dmsdocument/62251, ~1.4MB; topic index URL retained as it is stable). WorkSafe-set WES/BEI risk criteria for airborne hazardous substances; used for health risk assessment under the Hazardous Substances Regulations 2017. document_type=standard (WorkSafe-set exposure standard, NOT an ISO/AS-NZS standard) — so the crown-copyright-open licence DOES apply (unlike third-party AS/NZS standards). Mapped CHEMICAL. Attribution required.  [gap-review] Reclassified standard-&gt;guidance: free WorkSafe NZ Crown publication (NZ WES/BEI), not a paywalled ISO/AS standard.</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>NZ-GUI-005</t>
+          <t>NZ-GUI-004</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -61372,28 +61376,28 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>General risk and workplace management — Parts 1 &amp; 2 (WKS-3)</t>
+          <t>WorkSafe position on officers' due diligence</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
       <c r="G619" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/assets/dmsassets/WKS-3-general-risk-and-workplace-management-part-2.pdf</t>
+          <t>https://www.worksafe.govt.nz/dmsdocument/1058-worksafe-position-on-officers-due-diligence</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="K619" t="inlineStr"/>
@@ -61438,14 +61442,14 @@
       <c r="V619" t="inlineStr"/>
       <c r="W619" t="inlineStr">
         <is>
-          <t>Principal interpretive guidance for the GRWM Regs 2016 (NZ-REG-003).</t>
+          <t>s44 HSWA officer due-diligence standard of care.</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>NZ-STAT-001</t>
+          <t>NZ-GUI-005</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -61460,28 +61464,28 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>statistical_report</t>
+          <t>guidance</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Work health and safety: An overview of harm and risk in Aotearoa New Zealand 2024</t>
+          <t>General risk and workplace management — Parts 1 &amp; 2 (WKS-3)</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
       <c r="G620" t="inlineStr">
         <is>
-          <t>https://www.worksafe.govt.nz/research/work-health-and-safety-an-overview-of-harm-and-risk-in-aotearoa-new-zealand-2024/</t>
+          <t>https://www.worksafe.govt.nz/assets/dmsassets/WKS-3-general-risk-and-workplace-management-part-2.pdf</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
@@ -61489,11 +61493,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="K620" t="inlineStr"/>
       <c r="L620" t="inlineStr"/>
       <c r="M620" t="inlineStr"/>
       <c r="N620" t="inlineStr">
@@ -61513,7 +61513,7 @@
       </c>
       <c r="Q620" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R620" t="inlineStr">
@@ -61535,14 +61535,14 @@
       <c r="V620" t="inlineStr"/>
       <c r="W620" t="inlineStr">
         <is>
-          <t>Flagship NZ work-harm statistics report. Added per 2026-06-30 gap review.</t>
+          <t>Principal interpretive guidance for the GRWM Regs 2016 (NZ-REG-003).</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>NZ-STAT-002</t>
+          <t>NZ-STAT-001</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -61562,23 +61562,23 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>WorkSafe Data Centre — fatalities and work-related harm statistics</t>
+          <t>Work health and safety: An overview of harm and risk in Aotearoa New Zealand 2024</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
       <c r="G621" t="inlineStr">
         <is>
-          <t>https://data.worksafe.govt.nz/</t>
+          <t>https://www.worksafe.govt.nz/research/work-health-and-safety-an-overview-of-harm-and-risk-in-aotearoa-new-zealand-2024/</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
@@ -61586,12 +61586,16 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr"/>
       <c r="M621" t="inlineStr"/>
       <c r="N621" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O621" t="inlineStr">
@@ -61606,7 +61610,7 @@
       </c>
       <c r="Q621" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R621" t="inlineStr">
@@ -61628,55 +61632,55 @@
       <c r="V621" t="inlineStr"/>
       <c r="W621" t="inlineStr">
         <is>
-          <t>Canonical live NZ stats hub — snapshot/extract only (dashboard, not a discrete document).</t>
+          <t>Flagship NZ work-harm statistics report. Added per 2026-06-30 gap review.</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>AIHS-BOK-001</t>
+          <t>NZ-STAT-002</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>AIHS</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Australian Institute of Health &amp; Safety (AIHS)</t>
+          <t>WorkSafe New Zealand</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>bok_chapter</t>
+          <t>statistical_report</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>A problem-solving model of OHS practice</t>
+          <t>WorkSafe Data Centre — fatalities and work-related harm statistics</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
       <c r="G622" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-38-1-model-of-ohs-practice/</t>
+          <t>https://data.worksafe.govt.nz/</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="K622" t="inlineStr"/>
@@ -61684,7 +61688,7 @@
       <c r="M622" t="inlineStr"/>
       <c r="N622" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
@@ -61709,30 +61713,26 @@
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>proprietary-restricted-AIHS</t>
+          <t>crown-copyright-open-attribution</t>
         </is>
       </c>
       <c r="T622" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="U622" t="inlineStr">
-        <is>
-          <t>AIHS retains copyright; modification, republication or inclusion in another product/system requires express AIHS written permission (corporate/commercial licence). No ingestion or redistribution permitted absent that licence.</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr"/>
       <c r="V622" t="inlineStr"/>
       <c r="W622" t="inlineStr">
         <is>
-          <t>BoK Ch 37.2 (A problem-solving model of OHS practice). Live index labels 37.2 though slug carries 38-1. URL confirmed on live index.</t>
+          <t>Canonical live NZ stats hub — snapshot/extract only (dashboard, not a discrete document).</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>AIHS-BOK-002</t>
+          <t>AIHS-BOK-001</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -61752,13 +61752,13 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Appendix Organisational Culture: Thematic analysis of data from interviews and focus groups</t>
+          <t>A problem-solving model of OHS practice</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
       <c r="G623" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-10-2-1b-appendix-organisational-culture-thematic-analysis-of-data-from-interviews-and-focus-groups/</t>
+          <t>https://www.ohsbok.org.au/chapter-38-1-model-of-ohs-practice/</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -61822,14 +61822,14 @@
       <c r="V623" t="inlineStr"/>
       <c r="W623" t="inlineStr">
         <is>
-          <t>BoK Ch 10.2.1B (appendix). URL confirmed on live index.</t>
+          <t>BoK Ch 37.2 (A problem-solving model of OHS practice). Live index labels 37.2 though slug carries 38-1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>AIHS-BOK-003</t>
+          <t>AIHS-BOK-002</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -61849,13 +61849,13 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Biological Hazards</t>
+          <t>Appendix Organisational Culture: Thematic analysis of data from interviews and focus groups</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
       <c r="G624" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-18-biological-hazards/</t>
+          <t>https://www.ohsbok.org.au/chapter-10-2-1b-appendix-organisational-culture-thematic-analysis-of-data-from-interviews-and-focus-groups/</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -61873,11 +61873,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr"/>
       <c r="M624" t="inlineStr"/>
       <c r="N624" t="inlineStr">
@@ -61887,12 +61883,12 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>BIOLOGICAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P624" t="inlineStr">
         <is>
-          <t>HEALTH</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q624" t="inlineStr">
@@ -61923,14 +61919,14 @@
       <c r="V624" t="inlineStr"/>
       <c r="W624" t="inlineStr">
         <is>
-          <t>BoK Ch 18 Biological Hazards. No biological hazard_category in enum; mapped to CHEMICAL as nearest agent-exposure domain. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
+          <t>BoK Ch 10.2.1B (appendix). URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>AIHS-BOK-004</t>
+          <t>AIHS-BOK-003</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -61950,13 +61946,13 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Bullying and violence</t>
+          <t>Biological Hazards</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
       <c r="G625" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-21-psychosocial-hazards-bullying-aggression-and-violence/</t>
+          <t>https://www.ohsbok.org.au/chapter-18-biological-hazards/</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -61988,12 +61984,12 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>PSYCHOSOCIAL</t>
+          <t>BIOLOGICAL</t>
         </is>
       </c>
       <c r="P625" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>HEALTH</t>
         </is>
       </c>
       <c r="Q625" t="inlineStr">
@@ -62024,14 +62020,14 @@
       <c r="V625" t="inlineStr"/>
       <c r="W625" t="inlineStr">
         <is>
-          <t>BoK Ch 21 (Psychosocial hazards: Bullying, aggression and violence). Maps to PSYCHOSOCIAL per node rules. URL confirmed on live index.</t>
+          <t>BoK Ch 18 Biological Hazards. No biological hazard_category in enum; mapped to CHEMICAL as nearest agent-exposure domain. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>AIHS-BOK-005</t>
+          <t>AIHS-BOK-004</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -62051,13 +62047,13 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Chain of Responsibility</t>
+          <t>Bullying and violence</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-12-7-chain-of-responsibility/</t>
+          <t>https://www.ohsbok.org.au/chapter-21-psychosocial-hazards-bullying-aggression-and-violence/</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -62075,7 +62071,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr"/>
       <c r="M626" t="inlineStr"/>
       <c r="N626" t="inlineStr">
@@ -62085,12 +62085,12 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PSYCHOSOCIAL</t>
         </is>
       </c>
       <c r="P626" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q626" t="inlineStr">
@@ -62121,14 +62121,14 @@
       <c r="V626" t="inlineStr"/>
       <c r="W626" t="inlineStr">
         <is>
-          <t>BoK Ch 12.7 Chain of Responsibility (heavy-vehicle / road transport law). No TRANSPORT hazard_category in enum; mapped to GENERAL. URL confirmed on live index.</t>
+          <t>BoK Ch 21 (Psychosocial hazards: Bullying, aggression and violence). Maps to PSYCHOSOCIAL per node rules. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>AIHS-BOK-006</t>
+          <t>AIHS-BOK-005</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -62148,13 +62148,13 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Chemical Hazards</t>
+          <t>Chain of Responsibility</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-17-chemical-hazards/</t>
+          <t>https://www.ohsbok.org.au/chapter-12-7-chain-of-responsibility/</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -62172,11 +62172,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K627" t="inlineStr"/>
       <c r="L627" t="inlineStr"/>
       <c r="M627" t="inlineStr"/>
       <c r="N627" t="inlineStr">
@@ -62186,12 +62182,12 @@
       </c>
       <c r="O627" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P627" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TRANSPORT</t>
         </is>
       </c>
       <c r="Q627" t="inlineStr">
@@ -62222,14 +62218,14 @@
       <c r="V627" t="inlineStr"/>
       <c r="W627" t="inlineStr">
         <is>
-          <t>BoK Ch 17.1 Chemical Hazards. URL confirmed on live index.</t>
+          <t>BoK Ch 12.7 Chain of Responsibility (heavy-vehicle / road transport law). No TRANSPORT hazard_category in enum; mapped to GENERAL. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>AIHS-BOK-007</t>
+          <t>AIHS-BOK-006</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -62249,13 +62245,13 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Contents</t>
+          <t>Chemical Hazards</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-1-2-contents/</t>
+          <t>https://www.ohsbok.org.au/chapter-17-chemical-hazards/</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -62287,7 +62283,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P628" t="inlineStr">
@@ -62323,14 +62319,14 @@
       <c r="V628" t="inlineStr"/>
       <c r="W628" t="inlineStr">
         <is>
-          <t>BoK Ch 1.2. URL confirmed on live index.</t>
+          <t>BoK Ch 17.1 Chemical Hazards. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>AIHS-BOK-008</t>
+          <t>AIHS-BOK-007</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -62350,13 +62346,13 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Contractor Safety Management</t>
+          <t>Contents</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
       <c r="G629" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-12-4-contractor-management/</t>
+          <t>https://www.ohsbok.org.au/chapter-1-2-contents/</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -62374,7 +62370,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr"/>
       <c r="M629" t="inlineStr"/>
       <c r="N629" t="inlineStr">
@@ -62384,7 +62384,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>CONTRACTOR</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P629" t="inlineStr">
@@ -62420,14 +62420,14 @@
       <c r="V629" t="inlineStr"/>
       <c r="W629" t="inlineStr">
         <is>
-          <t>BoK Ch 12.4 Contractor Safety Management. URL confirmed on live index (listed as 'Contractor Safety Management').</t>
+          <t>BoK Ch 1.2. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>AIHS-BOK-009</t>
+          <t>AIHS-BOK-008</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -62447,13 +62447,13 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Design of work</t>
+          <t>Contractor Safety Management</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
       <c r="G630" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-34-4-work-design/</t>
+          <t>https://www.ohsbok.org.au/chapter-12-4-contractor-management/</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -62481,7 +62481,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CONTRACTOR</t>
         </is>
       </c>
       <c r="P630" t="inlineStr">
@@ -62517,14 +62517,14 @@
       <c r="V630" t="inlineStr"/>
       <c r="W630" t="inlineStr">
         <is>
-          <t>BoK Ch 34.4 Design of work. Index entry carried an anchor fragment; recorded clean base page URL — confirmed.</t>
+          <t>BoK Ch 12.4 Contractor Safety Management. URL confirmed on live index (listed as 'Contractor Safety Management').</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>AIHS-BOK-010</t>
+          <t>AIHS-BOK-009</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -62544,13 +62544,13 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Document Usability</t>
+          <t>Design of work</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
       <c r="G631" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/2333-2/</t>
+          <t>https://www.ohsbok.org.au/chapter-34-4-work-design/</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -62568,17 +62568,9 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr"/>
-      <c r="M631" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="M631" t="inlineStr"/>
       <c r="N631" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -62622,14 +62614,14 @@
       <c r="V631" t="inlineStr"/>
       <c r="W631" t="inlineStr">
         <is>
-          <t>BoK Ch 12.3.2. Non-standard slug /2333-2/ confirmed on live index.</t>
+          <t>BoK Ch 34.4 Design of work. Index entry carried an anchor fragment; recorded clean base page URL — confirmed.</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>AIHS-BOK-011</t>
+          <t>AIHS-BOK-010</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -62649,13 +62641,13 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Dusts, Fumes &amp; Fibres</t>
+          <t>Document Usability</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
       <c r="G632" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-17-3-dusts-fumes-fibres/</t>
+          <t>https://www.ohsbok.org.au/2333-2/</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -62673,9 +62665,17 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr"/>
-      <c r="M632" t="inlineStr"/>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="N632" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -62683,12 +62683,12 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P632" t="inlineStr">
         <is>
-          <t>CONSTRUCTION,MINING,MANUFACTURING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q632" t="inlineStr">
@@ -62719,14 +62719,14 @@
       <c r="V632" t="inlineStr"/>
       <c r="W632" t="inlineStr">
         <is>
-          <t>BoK Ch 17.3. Covers silica/RCS, asbestos fibres -&gt; CHEMICAL. URL confirmed on live index.</t>
+          <t>BoK Ch 12.3.2. Non-standard slug /2333-2/ confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>AIHS-BOK-012</t>
+          <t>AIHS-BOK-011</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -62746,13 +62746,13 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Dusts, Fumes &amp; Fibres</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
       <c r="G633" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-23-physical-hazards-electricity/</t>
+          <t>https://www.ohsbok.org.au/chapter-17-3-dusts-fumes-fibres/</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -62770,11 +62770,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K633" t="inlineStr"/>
       <c r="L633" t="inlineStr"/>
       <c r="M633" t="inlineStr"/>
       <c r="N633" t="inlineStr">
@@ -62784,12 +62780,12 @@
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>ELECTRICAL</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P633" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION,MINING,MANUFACTURING</t>
         </is>
       </c>
       <c r="Q633" t="inlineStr">
@@ -62820,14 +62816,14 @@
       <c r="V633" t="inlineStr"/>
       <c r="W633" t="inlineStr">
         <is>
-          <t>BoK Ch 23.1 Electricity. URL confirmed on live index.</t>
+          <t>BoK Ch 17.3. Covers silica/RCS, asbestos fibres -&gt; CHEMICAL. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>AIHS-BOK-013</t>
+          <t>AIHS-BOK-012</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -62847,13 +62843,13 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Electricity Appendix - Arc Flash</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
       <c r="G634" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-23-1-physical-hazards-electricity-appendix-arc-flash/</t>
+          <t>https://www.ohsbok.org.au/chapter-23-physical-hazards-electricity/</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -62871,7 +62867,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr"/>
       <c r="M634" t="inlineStr"/>
       <c r="N634" t="inlineStr">
@@ -62886,7 +62886,7 @@
       </c>
       <c r="P634" t="inlineStr">
         <is>
-          <t>MANUFACTURING,MINING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q634" t="inlineStr">
@@ -62917,14 +62917,14 @@
       <c r="V634" t="inlineStr"/>
       <c r="W634" t="inlineStr">
         <is>
-          <t>BoK Ch 23.2 Electricity Appendix (Arc Flash). URL confirmed on live index.</t>
+          <t>BoK Ch 23.1 Electricity. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>AIHS-BOK-014</t>
+          <t>AIHS-BOK-013</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -62944,13 +62944,13 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Emergency management</t>
+          <t>Electricity Appendix - Arc Flash</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
       <c r="G635" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-36-emergency-management/</t>
+          <t>https://www.ohsbok.org.au/chapter-23-1-physical-hazards-electricity-appendix-arc-flash/</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -62978,12 +62978,12 @@
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>ELECTRICAL</t>
         </is>
       </c>
       <c r="P635" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>MANUFACTURING,MINING</t>
         </is>
       </c>
       <c r="Q635" t="inlineStr">
@@ -63014,14 +63014,14 @@
       <c r="V635" t="inlineStr"/>
       <c r="W635" t="inlineStr">
         <is>
-          <t>BoK Ch 36 Emergency management. URL confirmed on live index.</t>
+          <t>BoK Ch 23.2 Electricity Appendix (Arc Flash). URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>AIHS-BOK-015</t>
+          <t>AIHS-BOK-014</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -63041,13 +63041,13 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Ethics and Professional Practice</t>
+          <t>Emergency management</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
       <c r="G636" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-38-3-ethics-and-professional-practice/</t>
+          <t>https://www.ohsbok.org.au/chapter-36-emergency-management/</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -63065,17 +63065,9 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="K636" t="inlineStr"/>
       <c r="L636" t="inlineStr"/>
-      <c r="M636" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="M636" t="inlineStr"/>
       <c r="N636" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -63119,14 +63111,14 @@
       <c r="V636" t="inlineStr"/>
       <c r="W636" t="inlineStr">
         <is>
-          <t>BoK Ch 38.3. URL confirmed on live index.</t>
+          <t>BoK Ch 36 Emergency management. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>AIHS-BOK-016</t>
+          <t>AIHS-BOK-015</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -63146,13 +63138,13 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Ethics and Professional Practice</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
       <c r="G637" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-20-psychosocial-hazards-fatigue/</t>
+          <t>https://www.ohsbok.org.au/chapter-38-3-ethics-and-professional-practice/</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -63172,11 +63164,15 @@
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="L637" t="inlineStr"/>
-      <c r="M637" t="inlineStr"/>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="N637" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -63184,7 +63180,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>PSYCHOSOCIAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P637" t="inlineStr">
@@ -63220,14 +63216,14 @@
       <c r="V637" t="inlineStr"/>
       <c r="W637" t="inlineStr">
         <is>
-          <t>BoK Ch 20 (Psychosocial hazards: Fatigue). URL confirmed on live index.</t>
+          <t>BoK Ch 38.3. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>AIHS-BOK-017</t>
+          <t>AIHS-BOK-016</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -63247,13 +63243,13 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Foreword, acknowledgments</t>
+          <t>Fatigue</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
       <c r="G638" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-1-1-foreword</t>
+          <t>https://www.ohsbok.org.au/chapter-20-psychosocial-hazards-fatigue/</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -63285,7 +63281,7 @@
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PSYCHOSOCIAL</t>
         </is>
       </c>
       <c r="P638" t="inlineStr">
@@ -63321,14 +63317,14 @@
       <c r="V638" t="inlineStr"/>
       <c r="W638" t="inlineStr">
         <is>
-          <t>BoK Ch 1.1. Confirmed present on live /bok-chapters/ index at this exact URL.</t>
+          <t>BoK Ch 20 (Psychosocial hazards: Fatigue). URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>AIHS-BOK-018</t>
+          <t>AIHS-BOK-017</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -63348,13 +63344,13 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Foundation Science</t>
+          <t>Foreword, acknowledgments</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-14-foundation-science/</t>
+          <t>https://www.ohsbok.org.au/chapter-1-1-foreword</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -63422,14 +63418,14 @@
       <c r="V639" t="inlineStr"/>
       <c r="W639" t="inlineStr">
         <is>
-          <t>BoK Ch 14 Foundation Science. URL confirmed on live index.</t>
+          <t>BoK Ch 1.1. Confirmed present on live /bok-chapters/ index at this exact URL.</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>AIHS-BOK-019</t>
+          <t>AIHS-BOK-018</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -63449,13 +63445,13 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Gravitational Hazards</t>
+          <t>Foundation Science</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-27-physical-hazards-gravitational/</t>
+          <t>https://www.ohsbok.org.au/chapter-14-foundation-science/</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -63487,12 +63483,12 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>FALLS</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P640" t="inlineStr">
         <is>
-          <t>CONSTRUCTION</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q640" t="inlineStr">
@@ -63523,14 +63519,14 @@
       <c r="V640" t="inlineStr"/>
       <c r="W640" t="inlineStr">
         <is>
-          <t>BoK Ch 27 Gravitational Hazards = working at height / falls -&gt; FALLS. URL confirmed on live index.</t>
+          <t>BoK Ch 14 Foundation Science. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>AIHS-BOK-020</t>
+          <t>AIHS-BOK-019</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -63550,13 +63546,13 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Guide to Investigations</t>
+          <t>Gravitational Hazards</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-12-6-2-guide-to-investigations/</t>
+          <t>https://www.ohsbok.org.au/chapter-27-physical-hazards-gravitational/</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -63574,7 +63570,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr"/>
       <c r="M641" t="inlineStr"/>
       <c r="N641" t="inlineStr">
@@ -63584,12 +63584,12 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FALLS</t>
         </is>
       </c>
       <c r="P641" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION</t>
         </is>
       </c>
       <c r="Q641" t="inlineStr">
@@ -63620,14 +63620,14 @@
       <c r="V641" t="inlineStr"/>
       <c r="W641" t="inlineStr">
         <is>
-          <t>BoK Ch 12.6.2 Guide to Investigations. URL confirmed on live index.</t>
+          <t>BoK Ch 27 Gravitational Hazards = working at height / falls -&gt; FALLS. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>AIHS-BOK-021</t>
+          <t>AIHS-BOK-020</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -63647,13 +63647,13 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Hazard as a Concept</t>
+          <t>Guide to Investigations</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
       <c r="G642" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-15-hazard-as-a-concept/</t>
+          <t>https://www.ohsbok.org.au/chapter-12-6-2-guide-to-investigations/</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -63671,11 +63671,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K642" t="inlineStr"/>
       <c r="L642" t="inlineStr"/>
       <c r="M642" t="inlineStr"/>
       <c r="N642" t="inlineStr">
@@ -63721,14 +63717,14 @@
       <c r="V642" t="inlineStr"/>
       <c r="W642" t="inlineStr">
         <is>
-          <t>BoK Ch 15 Hazard as a Concept. URL confirmed on live index.</t>
+          <t>BoK Ch 12.6.2 Guide to Investigations. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>AIHS-BOK-022</t>
+          <t>AIHS-BOK-021</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -63748,13 +63744,13 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Hazard as a Concept</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-6-1-global-concept-health/</t>
+          <t>https://www.ohsbok.org.au/chapter-15-hazard-as-a-concept/</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -63822,14 +63818,14 @@
       <c r="V643" t="inlineStr"/>
       <c r="W643" t="inlineStr">
         <is>
-          <t>BoK Ch 6 (Global concept: Health). URL confirmed on live index.</t>
+          <t>BoK Ch 15 Hazard as a Concept. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>AIHS-BOK-023</t>
+          <t>AIHS-BOK-022</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -63849,13 +63845,13 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Health and safety in design</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-34-3-health-and-safety-in-design/</t>
+          <t>https://www.ohsbok.org.au/chapter-6-1-global-concept-health/</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -63875,15 +63871,11 @@
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="L644" t="inlineStr"/>
-      <c r="M644" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="M644" t="inlineStr"/>
       <c r="N644" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -63927,14 +63919,14 @@
       <c r="V644" t="inlineStr"/>
       <c r="W644" t="inlineStr">
         <is>
-          <t>BoK Ch 34.3. URL confirmed on live index.</t>
+          <t>BoK Ch 6 (Global concept: Health). URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>AIHS-BOK-024</t>
+          <t>AIHS-BOK-023</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -63954,13 +63946,13 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Health effects of Hazardous Chemicals</t>
+          <t>Health and safety in design</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
       <c r="G645" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-17-2-health-effects-of-hazardous-chemicals/</t>
+          <t>https://www.ohsbok.org.au/chapter-34-3-health-and-safety-in-design/</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -63978,9 +63970,17 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr"/>
-      <c r="M645" t="inlineStr"/>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="N645" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -63988,7 +63988,7 @@
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P645" t="inlineStr">
@@ -64024,14 +64024,14 @@
       <c r="V645" t="inlineStr"/>
       <c r="W645" t="inlineStr">
         <is>
-          <t>BoK Ch 17.2. URL confirmed on live index.</t>
+          <t>BoK Ch 34.3. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>AIHS-BOK-025</t>
+          <t>AIHS-BOK-024</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -64051,13 +64051,13 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Heavy Vehicle Operations and Safety</t>
+          <t>Health effects of Hazardous Chemicals</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
       <c r="G646" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-17-2-health-effects-of-hazardous-chemicals/</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -64080,17 +64080,17 @@
       <c r="M646" t="inlineStr"/>
       <c r="N646" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>PLANT_EQUIPMENT</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P646" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q646" t="inlineStr">
@@ -64121,14 +64121,14 @@
       <c r="V646" t="inlineStr"/>
       <c r="W646" t="inlineStr">
         <is>
-          <t>BoK Ch 40.2. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
+          <t>BoK Ch 17.2. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>AIHS-BOK-026</t>
+          <t>AIHS-BOK-025</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -64148,23 +64148,23 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Heavy Vehicle Operations and Safety</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
       <c r="G647" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/foreword-acknowledgments/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>regulator_index</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
@@ -64172,26 +64172,22 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K647" t="inlineStr"/>
       <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr"/>
       <c r="N647" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLANT_EQUIPMENT</t>
         </is>
       </c>
       <c r="P647" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TRANSPORT</t>
         </is>
       </c>
       <c r="Q647" t="inlineStr">
@@ -64222,14 +64218,14 @@
       <c r="V647" t="inlineStr"/>
       <c r="W647" t="inlineStr">
         <is>
-          <t>BoK Ch 2 Introduction. Direct fetch HTTP 200 confirmed page header reads 'Chapter 2: Introduction' — the AIHS site quirk where Ch 2 lives at the /foreword-acknowledgments/ slug is verified, NOT an enumerator error.</t>
+          <t>BoK Ch 40.2. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>AIHS-BOK-027</t>
+          <t>AIHS-BOK-026</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -64249,23 +64245,23 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Introduction to 'practice' as a concept</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
       <c r="G648" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-37-introduction-to-practice-as-a-concept/</t>
+          <t>https://www.ohsbok.org.au/foreword-acknowledgments/</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
@@ -64273,7 +64269,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr"/>
       <c r="M648" t="inlineStr"/>
       <c r="N648" t="inlineStr">
@@ -64319,14 +64319,14 @@
       <c r="V648" t="inlineStr"/>
       <c r="W648" t="inlineStr">
         <is>
-          <t>BoK Ch 37.1. URL confirmed on live index.</t>
+          <t>BoK Ch 2 Introduction. Direct fetch HTTP 200 confirmed page header reads 'Chapter 2: Introduction' — the AIHS site quirk where Ch 2 lives at the /foreword-acknowledgments/ slug is verified, NOT an enumerator error.</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>AIHS-BOK-028</t>
+          <t>AIHS-BOK-027</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -64346,13 +64346,13 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Investigating Occupational Incidents and Crashes</t>
+          <t>Introduction to 'practice' as a concept</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
       <c r="G649" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-37-introduction-to-practice-as-a-concept/</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -64375,7 +64375,7 @@
       <c r="M649" t="inlineStr"/>
       <c r="N649" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
@@ -64385,7 +64385,7 @@
       </c>
       <c r="P649" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q649" t="inlineStr">
@@ -64416,14 +64416,14 @@
       <c r="V649" t="inlineStr"/>
       <c r="W649" t="inlineStr">
         <is>
-          <t>BoK Ch 40.5. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
+          <t>BoK Ch 37.1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>AIHS-BOK-029</t>
+          <t>AIHS-BOK-028</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -64443,13 +64443,13 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Investigations</t>
+          <t>Investigating Occupational Incidents and Crashes</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
       <c r="G650" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-12-6-1-investigations/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -64472,7 +64472,7 @@
       <c r="M650" t="inlineStr"/>
       <c r="N650" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
@@ -64482,7 +64482,7 @@
       </c>
       <c r="P650" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TRANSPORT</t>
         </is>
       </c>
       <c r="Q650" t="inlineStr">
@@ -64513,14 +64513,14 @@
       <c r="V650" t="inlineStr"/>
       <c r="W650" t="inlineStr">
         <is>
-          <t>BoK Ch 12.6.1 Investigations. URL confirmed on live index.</t>
+          <t>BoK Ch 40.5. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>AIHS-BOK-030</t>
+          <t>AIHS-BOK-029</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -64540,13 +64540,13 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Ionising Radiation</t>
+          <t>Investigations</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
       <c r="G651" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-24-physical-hazards-ionising-radiation/</t>
+          <t>https://www.ohsbok.org.au/chapter-12-6-1-investigations/</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -64564,11 +64564,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K651" t="inlineStr"/>
       <c r="L651" t="inlineStr"/>
       <c r="M651" t="inlineStr"/>
       <c r="N651" t="inlineStr">
@@ -64578,12 +64574,12 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>RADIATION</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P651" t="inlineStr">
         <is>
-          <t>HEALTH,MINING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q651" t="inlineStr">
@@ -64614,14 +64610,14 @@
       <c r="V651" t="inlineStr"/>
       <c r="W651" t="inlineStr">
         <is>
-          <t>BoK Ch 24 Ionising Radiation (physical hazard). No radiation category in enum; mapped to CHEMICAL as nearest agent-exposure domain. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
+          <t>BoK Ch 12.6.1 Investigations. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>AIHS-BOK-031</t>
+          <t>AIHS-BOK-030</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -64641,13 +64637,13 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Managing process safety</t>
+          <t>Ionising Radiation</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-12-3-managing-process-safety/</t>
+          <t>https://www.ohsbok.org.au/chapter-24-physical-hazards-ionising-radiation/</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -64665,7 +64661,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr"/>
       <c r="N652" t="inlineStr">
@@ -64675,12 +64675,12 @@
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>RADIATION</t>
         </is>
       </c>
       <c r="P652" t="inlineStr">
         <is>
-          <t>MANUFACTURING,MINING</t>
+          <t>HEALTH,MINING</t>
         </is>
       </c>
       <c r="Q652" t="inlineStr">
@@ -64711,14 +64711,14 @@
       <c r="V652" t="inlineStr"/>
       <c r="W652" t="inlineStr">
         <is>
-          <t>BoK Ch 13 'Managing process safety' (live index labels it Ch 13 though the slug carries 12-3). Process-safety / major hazard facilities. URL confirmed on live index.</t>
+          <t>BoK Ch 24 Ionising Radiation (physical hazard). No radiation category in enum; mapped to CHEMICAL as nearest agent-exposure domain. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>AIHS-BOK-032</t>
+          <t>AIHS-BOK-031</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -64738,13 +64738,13 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Mechanical Plant</t>
+          <t>Managing process safety</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-28-physical-hazards-plant/</t>
+          <t>https://www.ohsbok.org.au/chapter-12-3-managing-process-safety/</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -64762,11 +64762,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr">
@@ -64776,12 +64772,12 @@
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>PLANT_EQUIPMENT</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P653" t="inlineStr">
         <is>
-          <t>MANUFACTURING,CONSTRUCTION</t>
+          <t>MANUFACTURING,MINING</t>
         </is>
       </c>
       <c r="Q653" t="inlineStr">
@@ -64812,14 +64808,14 @@
       <c r="V653" t="inlineStr"/>
       <c r="W653" t="inlineStr">
         <is>
-          <t>BoK Ch 28 Mechanical Plant. URL confirmed on live index.</t>
+          <t>BoK Ch 13 'Managing process safety' (live index labels it Ch 13 though the slug carries 12-3). Process-safety / major hazard facilities. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>AIHS-BOK-033</t>
+          <t>AIHS-BOK-032</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -64839,13 +64835,13 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Mental Health and Well Being of Occupational Road Users</t>
+          <t>Mechanical Plant</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-28-physical-hazards-plant/</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -64863,22 +64859,26 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr"/>
       <c r="N654" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>PSYCHOSOCIAL</t>
+          <t>PLANT_EQUIPMENT</t>
         </is>
       </c>
       <c r="P654" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>MANUFACTURING,CONSTRUCTION</t>
         </is>
       </c>
       <c r="Q654" t="inlineStr">
@@ -64909,14 +64909,14 @@
       <c r="V654" t="inlineStr"/>
       <c r="W654" t="inlineStr">
         <is>
-          <t>BoK Ch 40.4. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
+          <t>BoK Ch 28 Mechanical Plant. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>AIHS-BOK-034</t>
+          <t>AIHS-BOK-033</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -64936,13 +64936,13 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Mitigation of health impacts</t>
+          <t>Mental Health and Well Being of Occupational Road Users</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
       <c r="G655" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-35-mitigation-health-impacts/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -64965,17 +64965,17 @@
       <c r="M655" t="inlineStr"/>
       <c r="N655" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PSYCHOSOCIAL</t>
         </is>
       </c>
       <c r="P655" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TRANSPORT</t>
         </is>
       </c>
       <c r="Q655" t="inlineStr">
@@ -65006,14 +65006,14 @@
       <c r="V655" t="inlineStr"/>
       <c r="W655" t="inlineStr">
         <is>
-          <t>BoK Ch 35 Mitigation of health impacts. URL confirmed on live index.</t>
+          <t>BoK Ch 40.4. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>AIHS-BOK-035</t>
+          <t>AIHS-BOK-034</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -65033,13 +65033,13 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Mobile Plant</t>
+          <t>Mitigation of health impacts</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
       <c r="G656" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-29-physical-hazards-mobile-plant/</t>
+          <t>https://www.ohsbok.org.au/chapter-35-mitigation-health-impacts/</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -65067,12 +65067,12 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>PLANT_EQUIPMENT</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P656" t="inlineStr">
         <is>
-          <t>CONSTRUCTION,MINING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q656" t="inlineStr">
@@ -65103,14 +65103,14 @@
       <c r="V656" t="inlineStr"/>
       <c r="W656" t="inlineStr">
         <is>
-          <t>BoK Ch 29 Mobile Plant. URL confirmed on live index.</t>
+          <t>BoK Ch 35 Mitigation of health impacts. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>AIHS-BOK-036</t>
+          <t>AIHS-BOK-035</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -65130,13 +65130,13 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Models of causation: Health determinants</t>
+          <t>Mobile Plant</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
       <c r="G657" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-33-models-of-causation-health-determinants/</t>
+          <t>https://www.ohsbok.org.au/chapter-29-physical-hazards-mobile-plant/</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -65154,11 +65154,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K657" t="inlineStr"/>
       <c r="L657" t="inlineStr"/>
       <c r="M657" t="inlineStr"/>
       <c r="N657" t="inlineStr">
@@ -65168,12 +65164,12 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLANT_EQUIPMENT</t>
         </is>
       </c>
       <c r="P657" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION,MINING</t>
         </is>
       </c>
       <c r="Q657" t="inlineStr">
@@ -65204,14 +65200,14 @@
       <c r="V657" t="inlineStr"/>
       <c r="W657" t="inlineStr">
         <is>
-          <t>BoK Ch 33 Models of causation: Health determinants. URL confirmed on live index.</t>
+          <t>BoK Ch 29 Mobile Plant. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>AIHS-BOK-037</t>
+          <t>AIHS-BOK-036</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -65231,13 +65227,13 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Models of causation: Safety</t>
+          <t>Models of causation: Health determinants</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
       <c r="G658" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-32-models-of-causation-safety/</t>
+          <t>https://www.ohsbok.org.au/chapter-33-models-of-causation-health-determinants/</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -65305,14 +65301,14 @@
       <c r="V658" t="inlineStr"/>
       <c r="W658" t="inlineStr">
         <is>
-          <t>BoK Ch 32 Models of causation: Safety. URL confirmed on live index.</t>
+          <t>BoK Ch 33 Models of causation: Health determinants. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>AIHS-BOK-038</t>
+          <t>AIHS-BOK-037</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -65332,13 +65328,13 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Non-Ionising Radiation – Electromagnetic</t>
+          <t>Models of causation: Safety</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
       <c r="G659" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-25-physical-hazards-non-ionising-radiation-electromagnetic/</t>
+          <t>https://www.ohsbok.org.au/chapter-32-models-of-causation-safety/</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -65356,7 +65352,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr"/>
       <c r="M659" t="inlineStr"/>
       <c r="N659" t="inlineStr">
@@ -65366,7 +65366,7 @@
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>RADIATION</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P659" t="inlineStr">
@@ -65402,14 +65402,14 @@
       <c r="V659" t="inlineStr"/>
       <c r="W659" t="inlineStr">
         <is>
-          <t>BoK Ch 25 Non-Ionising Radiation (physical hazard). No radiation category in enum; mapped to CHEMICAL as nearest agent-exposure domain. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
+          <t>BoK Ch 32 Models of causation: Safety. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>AIHS-BOK-039</t>
+          <t>AIHS-BOK-038</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -65429,13 +65429,13 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Occupational Noise</t>
+          <t>Non-Ionising Radiation – Electromagnetic</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
       <c r="G660" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-22-physical-hazards-noise-and-vibration/</t>
+          <t>https://www.ohsbok.org.au/chapter-25-physical-hazards-non-ionising-radiation-electromagnetic/</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -65453,11 +65453,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr"/>
       <c r="M660" t="inlineStr"/>
       <c r="N660" t="inlineStr">
@@ -65467,12 +65463,12 @@
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>NOISE</t>
+          <t>RADIATION</t>
         </is>
       </c>
       <c r="P660" t="inlineStr">
         <is>
-          <t>MANUFACTURING,CONSTRUCTION,MINING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q660" t="inlineStr">
@@ -65503,14 +65499,14 @@
       <c r="V660" t="inlineStr"/>
       <c r="W660" t="inlineStr">
         <is>
-          <t>BoK Ch 22.1 Occupational Noise (physical hazard). No NOISE category in enum; mapped to PLANT_EQUIPMENT as nearest physical-hazard domain. URL confirmed on live index.  [gap-review] Retagged NOISE (new hazard_category) to remove the split.</t>
+          <t>BoK Ch 25 Non-Ionising Radiation (physical hazard). No radiation category in enum; mapped to CHEMICAL as nearest agent-exposure domain. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>AIHS-BOK-040</t>
+          <t>AIHS-BOK-039</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -65530,13 +65526,13 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Occupational Road Use: A Holistic Overview</t>
+          <t>Occupational Noise</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
       <c r="G661" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-22-physical-hazards-noise-and-vibration/</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -65554,22 +65550,26 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr"/>
       <c r="M661" t="inlineStr"/>
       <c r="N661" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>PLANT_EQUIPMENT</t>
+          <t>NOISE</t>
         </is>
       </c>
       <c r="P661" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>MANUFACTURING,CONSTRUCTION,MINING</t>
         </is>
       </c>
       <c r="Q661" t="inlineStr">
@@ -65600,14 +65600,14 @@
       <c r="V661" t="inlineStr"/>
       <c r="W661" t="inlineStr">
         <is>
-          <t>BoK Ch 40.1. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey (surveymonkey.com/r/orupre), not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
+          <t>BoK Ch 22.1 Occupational Noise (physical hazard). No NOISE category in enum; mapped to PLANT_EQUIPMENT as nearest physical-hazard domain. URL confirmed on live index.  [gap-review] Retagged NOISE (new hazard_category) to remove the split.</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>AIHS-BOK-041</t>
+          <t>AIHS-BOK-040</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -65627,13 +65627,13 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>OHS Management Systems</t>
+          <t>Occupational Road Use: A Holistic Overview</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
       <c r="G662" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-12-2-ohs-management-systems/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -65651,26 +65651,22 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K662" t="inlineStr"/>
       <c r="L662" t="inlineStr"/>
       <c r="M662" t="inlineStr"/>
       <c r="N662" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLANT_EQUIPMENT</t>
         </is>
       </c>
       <c r="P662" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TRANSPORT</t>
         </is>
       </c>
       <c r="Q662" t="inlineStr">
@@ -65701,14 +65697,14 @@
       <c r="V662" t="inlineStr"/>
       <c r="W662" t="inlineStr">
         <is>
-          <t>BoK Ch 12.2. URL confirmed on live index.</t>
+          <t>BoK Ch 40.1. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey (surveymonkey.com/r/orupre), not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>AIHS-BOK-042</t>
+          <t>AIHS-BOK-041</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -65728,13 +65724,13 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>OHS risk and decision making</t>
+          <t>OHS Management Systems</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
       <c r="G663" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-31-2-ohs-risk-and-decision-making/</t>
+          <t>https://www.ohsbok.org.au/chapter-12-2-ohs-management-systems/</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -65752,7 +65748,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr"/>
       <c r="M663" t="inlineStr"/>
       <c r="N663" t="inlineStr">
@@ -65798,14 +65798,14 @@
       <c r="V663" t="inlineStr"/>
       <c r="W663" t="inlineStr">
         <is>
-          <t>BoK Ch 31.2 OHS risk and decision making. URL confirmed on live index.</t>
+          <t>BoK Ch 12.2. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>AIHS-BOK-043</t>
+          <t>AIHS-BOK-042</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -65825,13 +65825,13 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Organisational Culture: A Search for Meaning</t>
+          <t>OHS risk and decision making</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
       <c r="G664" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-10-2-1-organisational-culture-a-search-for-meaning/</t>
+          <t>https://www.ohsbok.org.au/chapter-31-2-ohs-risk-and-decision-making/</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -65895,14 +65895,14 @@
       <c r="V664" t="inlineStr"/>
       <c r="W664" t="inlineStr">
         <is>
-          <t>BoK Ch 10.2.1. URL confirmed on live index.</t>
+          <t>BoK Ch 31.2 OHS risk and decision making. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>AIHS-BOK-044</t>
+          <t>AIHS-BOK-043</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -65922,13 +65922,13 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Organisational Culture: Reviewed and Repositioned</t>
+          <t>Organisational Culture: A Search for Meaning</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
       <c r="G665" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/2117-2/</t>
+          <t>https://www.ohsbok.org.au/chapter-10-2-1-organisational-culture-a-search-for-meaning/</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -65992,14 +65992,14 @@
       <c r="V665" t="inlineStr"/>
       <c r="W665" t="inlineStr">
         <is>
-          <t>BoK Ch 10.2.2. Index lists this at /2117-2/ (with an anchor fragment); recorded clean base page URL — confirmed.</t>
+          <t>BoK Ch 10.2.1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>AIHS-BOK-045</t>
+          <t>AIHS-BOK-044</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -66019,13 +66019,13 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Prevention and intervention</t>
+          <t>Organisational Culture: Reviewed and Repositioned</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
       <c r="G666" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-34-1-control-prevention-and-intervention/</t>
+          <t>https://www.ohsbok.org.au/2117-2/</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -66043,11 +66043,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K666" t="inlineStr"/>
       <c r="L666" t="inlineStr"/>
       <c r="M666" t="inlineStr"/>
       <c r="N666" t="inlineStr">
@@ -66093,14 +66089,14 @@
       <c r="V666" t="inlineStr"/>
       <c r="W666" t="inlineStr">
         <is>
-          <t>BoK Ch 34.1 Control: Prevention and intervention (hierarchy of control). URL confirmed on live index.</t>
+          <t>BoK Ch 10.2.2. Index lists this at /2117-2/ (with an anchor fragment); recorded clean base page URL — confirmed.</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>AIHS-BOK-046</t>
+          <t>AIHS-BOK-045</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -66120,13 +66116,13 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Process Hazards (Chemical)</t>
+          <t>Prevention and intervention</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
       <c r="G667" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-17-3-process-hazards-chemical/</t>
+          <t>https://www.ohsbok.org.au/chapter-34-1-control-prevention-and-intervention/</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -66144,7 +66140,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr"/>
       <c r="M667" t="inlineStr"/>
       <c r="N667" t="inlineStr">
@@ -66154,12 +66154,12 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P667" t="inlineStr">
         <is>
-          <t>MANUFACTURING,MINING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q667" t="inlineStr">
@@ -66190,14 +66190,14 @@
       <c r="V667" t="inlineStr"/>
       <c r="W667" t="inlineStr">
         <is>
-          <t>BoK Ch 17.4 Process Hazards (Chemical). Live index labels it 17.4 though slug carries 17-3. URL confirmed on live index.</t>
+          <t>BoK Ch 34.1 Control: Prevention and intervention (hierarchy of control). URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>AIHS-BOK-047</t>
+          <t>AIHS-BOK-046</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -66217,23 +66217,23 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Psychosocial hazards</t>
+          <t>Process Hazards (Chemical)</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
       <c r="G668" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-19-psychosocial-hazards/</t>
+          <t>https://www.ohsbok.org.au/chapter-17-3-process-hazards-chemical/</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>regulator_index</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
@@ -66241,17 +66241,9 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K668" t="inlineStr"/>
       <c r="L668" t="inlineStr"/>
-      <c r="M668" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
+      <c r="M668" t="inlineStr"/>
       <c r="N668" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -66259,12 +66251,12 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>PSYCHOSOCIAL</t>
+          <t>CHEMICAL</t>
         </is>
       </c>
       <c r="P668" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>MANUFACTURING,MINING</t>
         </is>
       </c>
       <c r="Q668" t="inlineStr">
@@ -66295,14 +66287,14 @@
       <c r="V668" t="inlineStr"/>
       <c r="W668" t="inlineStr">
         <is>
-          <t>BoK Ch 19. Direct fetch HTTP 200; page header 'Chapter 19: Psychosocial Hazards'; current version 2020 (first published 2012), 2012 archive also offered. Re-confirmed.</t>
+          <t>BoK Ch 17.4 Process Hazards (Chemical). Live index labels it 17.4 though slug carries 17-3. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>AIHS-BOK-048</t>
+          <t>AIHS-BOK-047</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -66322,23 +66314,23 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Psychosocial hazards</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
       <c r="G669" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-31-1-risk/</t>
+          <t>https://www.ohsbok.org.au/chapter-19-psychosocial-hazards/</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
@@ -66352,7 +66344,11 @@
         </is>
       </c>
       <c r="L669" t="inlineStr"/>
-      <c r="M669" t="inlineStr"/>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="N669" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -66360,7 +66356,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PSYCHOSOCIAL</t>
         </is>
       </c>
       <c r="P669" t="inlineStr">
@@ -66396,14 +66392,14 @@
       <c r="V669" t="inlineStr"/>
       <c r="W669" t="inlineStr">
         <is>
-          <t>BoK Ch 31.1 Risk. URL confirmed on live index.</t>
+          <t>BoK Ch 19. Direct fetch HTTP 200; page header 'Chapter 19: Psychosocial Hazards'; current version 2020 (first published 2012), 2012 archive also offered. Re-confirmed.</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>AIHS-BOK-049</t>
+          <t>AIHS-BOK-048</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -66423,13 +66419,13 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Rules and procedures</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
       <c r="G670" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/rulesandprocedures/</t>
+          <t>https://www.ohsbok.org.au/chapter-31-1-risk/</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -66447,7 +66443,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr"/>
       <c r="M670" t="inlineStr"/>
       <c r="N670" t="inlineStr">
@@ -66493,14 +66493,14 @@
       <c r="V670" t="inlineStr"/>
       <c r="W670" t="inlineStr">
         <is>
-          <t>BoK Ch 12.3.1. Non-standard slug /rulesandprocedures/ confirmed on live index.</t>
+          <t>BoK Ch 31.1 Risk. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>AIHS-BOK-050</t>
+          <t>AIHS-BOK-049</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -66520,13 +66520,13 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Rules and procedures</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
       <c r="G671" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-5-1-global-concept-safety/</t>
+          <t>https://www.ohsbok.org.au/rulesandprocedures/</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -66544,11 +66544,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K671" t="inlineStr"/>
       <c r="L671" t="inlineStr"/>
       <c r="M671" t="inlineStr"/>
       <c r="N671" t="inlineStr">
@@ -66594,14 +66590,14 @@
       <c r="V671" t="inlineStr"/>
       <c r="W671" t="inlineStr">
         <is>
-          <t>BoK Ch 5 (Global concept: Safety). URL confirmed on live index.</t>
+          <t>BoK Ch 12.3.1. Non-standard slug /rulesandprocedures/ confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>AIHS-BOK-051</t>
+          <t>AIHS-BOK-050</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -66621,13 +66617,13 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Safety for Vulnerable Road Users</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
       <c r="G672" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-5-1-global-concept-safety/</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -66645,22 +66641,26 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr"/>
       <c r="M672" t="inlineStr"/>
       <c r="N672" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>PLANT_EQUIPMENT</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P672" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q672" t="inlineStr">
@@ -66691,14 +66691,14 @@
       <c r="V672" t="inlineStr"/>
       <c r="W672" t="inlineStr">
         <is>
-          <t>BoK Ch 40.3. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
+          <t>BoK Ch 5 (Global concept: Safety). URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>AIHS-BOK-052</t>
+          <t>AIHS-BOK-051</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -66718,13 +66718,13 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Socio-political context: OHS law and regulation in Australia</t>
+          <t>Safety for Vulnerable Road Users</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
       <c r="G673" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-9-1-socio-political-context-ohs-law-and-regulation-in-australia/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -66742,26 +66742,22 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K673" t="inlineStr"/>
       <c r="L673" t="inlineStr"/>
       <c r="M673" t="inlineStr"/>
       <c r="N673" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PLANT_EQUIPMENT</t>
         </is>
       </c>
       <c r="P673" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TRANSPORT</t>
         </is>
       </c>
       <c r="Q673" t="inlineStr">
@@ -66792,14 +66788,14 @@
       <c r="V673" t="inlineStr"/>
       <c r="W673" t="inlineStr">
         <is>
-          <t>BoK Ch 9.1. Title aligned to official slug. URL confirmed on live index.</t>
+          <t>BoK Ch 40.3. CONFIRMED on live index: links to a SurveyMonkey pre-publication survey, not a published chapter; NOT yet published. URL set to verified /bok-chapters/ index. Re-VERIFY at build time.</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>AIHS-BOK-053</t>
+          <t>AIHS-BOK-052</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -66819,13 +66815,13 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Synopsis of the OHS Body of Knowledge</t>
+          <t>Socio-political context: OHS law and regulation in Australia</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
       <c r="G674" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-1-3-synopsis-of-the-ohs-body-of-knowledge/</t>
+          <t>https://www.ohsbok.org.au/chapter-9-1-socio-political-context-ohs-law-and-regulation-in-australia/</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -66893,14 +66889,14 @@
       <c r="V674" t="inlineStr"/>
       <c r="W674" t="inlineStr">
         <is>
-          <t>BoK Ch 1.3. URL confirmed on live index.</t>
+          <t>BoK Ch 9.1. Title aligned to official slug. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>AIHS-BOK-054</t>
+          <t>AIHS-BOK-053</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -66920,13 +66916,13 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Systems</t>
+          <t>Synopsis of the OHS Body of Knowledge</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
       <c r="G675" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-12-1-systems/</t>
+          <t>https://www.ohsbok.org.au/chapter-1-3-synopsis-of-the-ohs-body-of-knowledge/</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -66994,14 +66990,14 @@
       <c r="V675" t="inlineStr"/>
       <c r="W675" t="inlineStr">
         <is>
-          <t>BoK Ch 12.1. URL confirmed on live index.</t>
+          <t>BoK Ch 1.3. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>AIHS-BOK-055</t>
+          <t>AIHS-BOK-054</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -67021,23 +67017,23 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>The Core Body of Knowledge for Generalist OHS Professionals, 3rd Edition</t>
+          <t>Systems</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
       <c r="G676" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-12-1-systems/</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>direct_fetch</t>
+          <t>regulator_index</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
@@ -67047,15 +67043,11 @@
       </c>
       <c r="K676" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="L676" t="inlineStr"/>
-      <c r="M676" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="M676" t="inlineStr"/>
       <c r="N676" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -67099,14 +67091,14 @@
       <c r="V676" t="inlineStr"/>
       <c r="W676" t="inlineStr">
         <is>
-          <t>Whole-of-work parent reference: 'The Core Body of Knowledge for Generalist OHS Professionals, 3rd Edition' (AIHS, 2024). Prescribed citation CONFIRMED via /accessing-and-using/: 'Safety Institute of Australia. (2024). The Core Body of Knowledge for Generalist OHS Professionals, 3rd Edition. Kensington, VIC: Australian Institute of Health and Safety.' URL = verified /bok-chapters/ index landing.</t>
+          <t>BoK Ch 12.1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>AIHS-BOK-056</t>
+          <t>AIHS-BOK-055</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -67126,23 +67118,23 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>The Generalist OHS Professional in Australia</t>
+          <t>The Core Body of Knowledge for Generalist OHS Professionals, 3rd Edition</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
       <c r="G677" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-3-1-the-generalist-ohs-professional-in-australia-2012/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>regulator_index</t>
+          <t>direct_fetch</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
@@ -67152,11 +67144,15 @@
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="L677" t="inlineStr"/>
-      <c r="M677" t="inlineStr"/>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="N677" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -67200,14 +67196,14 @@
       <c r="V677" t="inlineStr"/>
       <c r="W677" t="inlineStr">
         <is>
-          <t>BoK Ch 3. Title corrected to match the official slug/index entry 'The Generalist OHS Professional in Australia' (enumerator's 'International and Australian Perspectives' subtitle not on the live index). URL confirmed.</t>
+          <t>Whole-of-work parent reference: 'The Core Body of Knowledge for Generalist OHS Professionals, 3rd Edition' (AIHS, 2024). Prescribed citation CONFIRMED via /accessing-and-using/: 'Safety Institute of Australia. (2024). The Core Body of Knowledge for Generalist OHS Professionals, 3rd Edition. Kensington, VIC: Australian Institute of Health and Safety.' URL = verified /bok-chapters/ index landing.</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>AIHS-BOK-057</t>
+          <t>AIHS-BOK-056</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -67227,13 +67223,13 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>The Human: As a Biological System</t>
+          <t>The Generalist OHS Professional in Australia</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
       <c r="G678" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-7-the-human-as-a-biological-system/</t>
+          <t>https://www.ohsbok.org.au/chapter-3-1-the-generalist-ohs-professional-in-australia-2012/</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -67301,14 +67297,14 @@
       <c r="V678" t="inlineStr"/>
       <c r="W678" t="inlineStr">
         <is>
-          <t>BoK Ch 7.1. URL confirmed on live index.</t>
+          <t>BoK Ch 3. Title corrected to match the official slug/index entry 'The Generalist OHS Professional in Australia' (enumerator's 'International and Australian Perspectives' subtitle not on the live index). URL confirmed.</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>AIHS-BOK-058</t>
+          <t>AIHS-BOK-057</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -67328,13 +67324,13 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>The Human: Basic principles of social interaction</t>
+          <t>The Human: As a Biological System</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
       <c r="G679" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-8-2-the-human-basic-principles-of-social-interaction/</t>
+          <t>https://www.ohsbok.org.au/chapter-7-the-human-as-a-biological-system/</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -67366,7 +67362,7 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>PSYCHOSOCIAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P679" t="inlineStr">
@@ -67402,14 +67398,14 @@
       <c r="V679" t="inlineStr"/>
       <c r="W679" t="inlineStr">
         <is>
-          <t>BoK Ch 8.2. URL confirmed on live index.</t>
+          <t>BoK Ch 7.1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>AIHS-BOK-059</t>
+          <t>AIHS-BOK-058</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -67429,13 +67425,13 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>The Human: Basic psychological principles</t>
+          <t>The Human: Basic principles of social interaction</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
       <c r="G680" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-8-1-the-human-basic-psychological-principles/</t>
+          <t>https://www.ohsbok.org.au/chapter-8-2-the-human-basic-principles-of-social-interaction/</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -67503,14 +67499,14 @@
       <c r="V680" t="inlineStr"/>
       <c r="W680" t="inlineStr">
         <is>
-          <t>BoK Ch 8.1. URL confirmed on live index.</t>
+          <t>BoK Ch 8.2. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>AIHS-BOK-060</t>
+          <t>AIHS-BOK-059</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -67530,13 +67526,13 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>The OHS professional as a 'critical consumer' of research</t>
+          <t>The Human: Basic psychological principles</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
       <c r="G681" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-39-1-the-ohs-professional-as-a-critical-consumer-of-research/</t>
+          <t>https://www.ohsbok.org.au/chapter-8-1-the-human-basic-psychological-principles/</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -67554,7 +67550,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr"/>
       <c r="M681" t="inlineStr"/>
       <c r="N681" t="inlineStr">
@@ -67564,7 +67564,7 @@
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PSYCHOSOCIAL</t>
         </is>
       </c>
       <c r="P681" t="inlineStr">
@@ -67600,14 +67600,14 @@
       <c r="V681" t="inlineStr"/>
       <c r="W681" t="inlineStr">
         <is>
-          <t>BoK Ch 39.1. URL confirmed on live index.</t>
+          <t>BoK Ch 8.1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>AIHS-BOK-061</t>
+          <t>AIHS-BOK-060</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -67627,13 +67627,13 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>The OHS Professional as a Workplace Influencer</t>
+          <t>The OHS professional as a 'critical consumer' of research</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
       <c r="G682" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-39-1-the-ohs-professional-as-a-critical-consumer-of-research/</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -67656,7 +67656,7 @@
       <c r="M682" t="inlineStr"/>
       <c r="N682" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
@@ -67697,14 +67697,14 @@
       <c r="V682" t="inlineStr"/>
       <c r="W682" t="inlineStr">
         <is>
-          <t>BoK Ch 39.3. CONFIRMED on live index as 'Coming Soon' — NOT yet published. URL set to verified /bok-chapters/ index; individual chapter URL does not yet exist. Re-VERIFY at build time.</t>
+          <t>BoK Ch 39.1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>AIHS-BOK-062</t>
+          <t>AIHS-BOK-061</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -67724,13 +67724,13 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>The Organisation</t>
+          <t>The OHS Professional as a Workplace Influencer</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
       <c r="G683" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-10-1-the-organisation/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -67748,20 +67748,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K683" t="inlineStr"/>
       <c r="L683" t="inlineStr"/>
-      <c r="M683" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="M683" t="inlineStr"/>
       <c r="N683" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="O683" t="inlineStr">
@@ -67802,14 +67794,14 @@
       <c r="V683" t="inlineStr"/>
       <c r="W683" t="inlineStr">
         <is>
-          <t>BoK Ch 10.1. URL confirmed on live index.</t>
+          <t>BoK Ch 39.3. CONFIRMED on live index as 'Coming Soon' — NOT yet published. URL set to verified /bok-chapters/ index; individual chapter URL does not yet exist. Re-VERIFY at build time.</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>AIHS-BOK-063</t>
+          <t>AIHS-BOK-062</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -67829,13 +67821,13 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Thermal Environment</t>
+          <t>The Organisation</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
       <c r="G684" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-26-physical-hazards-thermal-environment/</t>
+          <t>https://www.ohsbok.org.au/chapter-10-1-the-organisation/</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -67853,9 +67845,17 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr"/>
-      <c r="M684" t="inlineStr"/>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="N684" t="inlineStr">
         <is>
           <t>CURRENT</t>
@@ -67863,12 +67863,12 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>THERMAL</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P684" t="inlineStr">
         <is>
-          <t>CONSTRUCTION,MINING,MANUFACTURING</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q684" t="inlineStr">
@@ -67899,14 +67899,14 @@
       <c r="V684" t="inlineStr"/>
       <c r="W684" t="inlineStr">
         <is>
-          <t>BoK Ch 26 Thermal Environment (heat/cold stress). No thermal category in enum; mapped to GENERAL. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
+          <t>BoK Ch 10.1. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>AIHS-BOK-064</t>
+          <t>AIHS-BOK-063</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -67926,13 +67926,13 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>User-Centered Safe Design approach to control</t>
+          <t>Thermal Environment</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
       <c r="G685" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-34-2-user-centred-safe-design-approach-to-control/</t>
+          <t>https://www.ohsbok.org.au/chapter-26-physical-hazards-thermal-environment/</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -67960,12 +67960,12 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>THERMAL</t>
         </is>
       </c>
       <c r="P685" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION,MINING,MANUFACTURING</t>
         </is>
       </c>
       <c r="Q685" t="inlineStr">
@@ -67996,14 +67996,14 @@
       <c r="V685" t="inlineStr"/>
       <c r="W685" t="inlineStr">
         <is>
-          <t>BoK Ch 34.2. URL confirmed on live index.</t>
+          <t>BoK Ch 26 Thermal Environment (heat/cold stress). No thermal category in enum; mapped to GENERAL. URL confirmed on live index.  [gap-review] hazard_category corrected (physical-agent / methodology mis-tag).</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>AIHS-BOK-065</t>
+          <t>AIHS-BOK-064</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -68023,13 +68023,13 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Vehicles and occupational road use</t>
+          <t>User-Centered Safe Design approach to control</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
       <c r="G686" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-30-physical-hazards-vehicles-and-occupational-road-use/</t>
+          <t>https://www.ohsbok.org.au/chapter-34-2-user-centred-safe-design-approach-to-control/</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -68057,12 +68057,12 @@
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>PLANT_EQUIPMENT</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P686" t="inlineStr">
         <is>
-          <t>TRANSPORT</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="Q686" t="inlineStr">
@@ -68093,14 +68093,14 @@
       <c r="V686" t="inlineStr"/>
       <c r="W686" t="inlineStr">
         <is>
-          <t>BoK Ch 30 Vehicles and occupational road use. No TRANSPORT hazard category; mapped to PLANT_EQUIPMENT (vehicle as plant). URL confirmed on live index.</t>
+          <t>BoK Ch 34.2. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>AIHS-BOK-066</t>
+          <t>AIHS-BOK-065</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -68120,13 +68120,13 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Vibration</t>
+          <t>Vehicles and occupational road use</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
       <c r="G687" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-22-2-vibration/</t>
+          <t>https://www.ohsbok.org.au/chapter-30-physical-hazards-vehicles-and-occupational-road-use/</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -68154,12 +68154,12 @@
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>NOISE</t>
+          <t>PLANT_EQUIPMENT</t>
         </is>
       </c>
       <c r="P687" t="inlineStr">
         <is>
-          <t>CONSTRUCTION,MINING,TRANSPORT</t>
+          <t>TRANSPORT</t>
         </is>
       </c>
       <c r="Q687" t="inlineStr">
@@ -68190,14 +68190,14 @@
       <c r="V687" t="inlineStr"/>
       <c r="W687" t="inlineStr">
         <is>
-          <t>BoK Ch 22.2 Vibration (physical hazard). URL confirmed on live index.  [gap-review] Retagged NOISE (new hazard_category) to remove the split.</t>
+          <t>BoK Ch 30 Vehicles and occupational road use. No TRANSPORT hazard category; mapped to PLANT_EQUIPMENT (vehicle as plant). URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>AIHS-BOK-067</t>
+          <t>AIHS-BOK-066</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -68217,13 +68217,13 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Vibration</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
       <c r="G688" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/bok-chapters/</t>
+          <t>https://www.ohsbok.org.au/chapter-22-2-vibration/</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -68246,17 +68246,17 @@
       <c r="M688" t="inlineStr"/>
       <c r="N688" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NOISE</t>
         </is>
       </c>
       <c r="P688" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CONSTRUCTION,MINING,TRANSPORT</t>
         </is>
       </c>
       <c r="Q688" t="inlineStr">
@@ -68287,14 +68287,14 @@
       <c r="V688" t="inlineStr"/>
       <c r="W688" t="inlineStr">
         <is>
-          <t>BoK Ch 4 Work. CONFIRMED on live /bok-chapters/ index the 'Work' entry links to a generic /chapter-download-template/ page (no stable chapter URL). Using verified /bok-chapters/ index landing. Individual chapter URL unresolved - VERIFY at build time.</t>
+          <t>BoK Ch 22.2 Vibration (physical hazard). URL confirmed on live index.  [gap-review] Retagged NOISE (new hazard_category) to remove the split.</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>AIHS-BOK-068</t>
+          <t>AIHS-BOK-067</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -68314,13 +68314,13 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Work Health and Safety Law in Australia</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
       <c r="G689" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-9-2-work-health-and-safety-law-in-australia/</t>
+          <t>https://www.ohsbok.org.au/bok-chapters/</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -68338,16 +68338,12 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+      <c r="K689" t="inlineStr"/>
       <c r="L689" t="inlineStr"/>
       <c r="M689" t="inlineStr"/>
       <c r="N689" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
@@ -68388,14 +68384,14 @@
       <c r="V689" t="inlineStr"/>
       <c r="W689" t="inlineStr">
         <is>
-          <t>BoK Ch 9.2. Describes the harmonised model WHS framework and flags WA non-harmonisation in-text. URL confirmed on live index.</t>
+          <t>BoK Ch 4 Work. CONFIRMED on live /bok-chapters/ index the 'Work' entry links to a generic /chapter-download-template/ page (no stable chapter URL). Using verified /bok-chapters/ index landing. Individual chapter URL unresolved - VERIFY at build time.</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>AIHS-BOK-069</t>
+          <t>AIHS-BOK-068</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -68415,13 +68411,13 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Work-related Musculoskeletal Disorders</t>
+          <t>Work Health and Safety Law in Australia</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
       <c r="G690" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/chapter-16-workrelated-musculoskeletal_disorders/</t>
+          <t>https://www.ohsbok.org.au/chapter-9-2-work-health-and-safety-law-in-australia/</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -68453,7 +68449,7 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>MANUAL_HANDLING</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="P690" t="inlineStr">
@@ -68489,14 +68485,14 @@
       <c r="V690" t="inlineStr"/>
       <c r="W690" t="inlineStr">
         <is>
-          <t>BoK Ch 16 (biomechanical hazards / hazardous manual tasks). URL confirmed on live index.</t>
+          <t>BoK Ch 9.2. Describes the harmonised model WHS framework and flags WA non-harmonisation in-text. URL confirmed on live index.</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>AIHS-BOK-070</t>
+          <t>AIHS-BOK-069</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -68516,13 +68512,13 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Workers Working from Home</t>
+          <t>Work-related Musculoskeletal Disorders</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
       <c r="G691" t="inlineStr">
         <is>
-          <t>https://www.ohsbok.org.au/2231-2/</t>
+          <t>https://www.ohsbok.org.au/chapter-16-workrelated-musculoskeletal_disorders/</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -68540,7 +68536,11 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr"/>
       <c r="M691" t="inlineStr"/>
       <c r="N691" t="inlineStr">
@@ -68550,7 +68550,7 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>MANUAL_HANDLING</t>
         </is>
       </c>
       <c r="P691" t="inlineStr">
@@ -68586,12 +68586,109 @@
       <c r="V691" t="inlineStr"/>
       <c r="W691" t="inlineStr">
         <is>
+          <t>BoK Ch 16 (biomechanical hazards / hazardous manual tasks). URL confirmed on live index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>AIHS-BOK-070</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>AIHS</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Australian Institute of Health &amp; Safety (AIHS)</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>bok_chapter</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Workers Working from Home</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://www.ohsbok.org.au/2231-2/</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>regulator_index</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr"/>
+      <c r="L692" t="inlineStr"/>
+      <c r="M692" t="inlineStr"/>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>proprietary-restricted-AIHS</t>
+        </is>
+      </c>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>AIHS retains copyright; modification, republication or inclusion in another product/system requires express AIHS written permission (corporate/commercial licence). No ingestion or redistribution permitted absent that licence.</t>
+        </is>
+      </c>
+      <c r="V692" t="inlineStr"/>
+      <c r="W692" t="inlineStr">
+        <is>
           <t>BoK Ch 37.4 Workers Working from Home. Non-standard slug /2231-2/ confirmed on live index.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W691"/>
+  <autoFilter ref="A1:W692"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>